--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122962156</v>
+        <v>122970496</v>
       </c>
       <c r="B2" t="n">
         <v>90962</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372213</v>
+        <v>372318</v>
       </c>
       <c r="R2" t="n">
-        <v>6934190</v>
+        <v>6934300</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122970496</v>
+        <v>122962156</v>
       </c>
       <c r="B3" t="n">
         <v>90962</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372318</v>
+        <v>372213</v>
       </c>
       <c r="R3" t="n">
-        <v>6934300</v>
+        <v>6934190</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122968306</v>
+        <v>122960937</v>
       </c>
       <c r="B6" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372375</v>
+        <v>372056</v>
       </c>
       <c r="R6" t="n">
-        <v>6934215</v>
+        <v>6934270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122960937</v>
+        <v>122961588</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372056</v>
+        <v>372194</v>
       </c>
       <c r="R7" t="n">
-        <v>6934270</v>
+        <v>6934243</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122961588</v>
+        <v>122968306</v>
       </c>
       <c r="B8" t="n">
-        <v>90944</v>
+        <v>82553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372194</v>
+        <v>372375</v>
       </c>
       <c r="R8" t="n">
-        <v>6934243</v>
+        <v>6934215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122969456</v>
+        <v>122965070</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,37 +1512,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372175</v>
+        <v>372491</v>
       </c>
       <c r="R10" t="n">
-        <v>6934323</v>
+        <v>6934104</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122965070</v>
+        <v>122969456</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,42 +1619,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372491</v>
+        <v>372175</v>
       </c>
       <c r="R11" t="n">
-        <v>6934104</v>
+        <v>6934323</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122960569</v>
+        <v>122965818</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1945,14 +1945,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372015</v>
+        <v>372684</v>
       </c>
       <c r="R14" t="n">
-        <v>6934298</v>
+        <v>6934056</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122965818</v>
+        <v>122960569</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2047,14 +2047,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372684</v>
+        <v>372015</v>
       </c>
       <c r="R15" t="n">
-        <v>6934056</v>
+        <v>6934298</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -4775,7 +4775,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122961215</v>
+        <v>122968318</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>372104</v>
+        <v>372375</v>
       </c>
       <c r="R42" t="n">
-        <v>6934254</v>
+        <v>6934215</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122965816</v>
+        <v>122967925</v>
       </c>
       <c r="B43" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4893,34 +4893,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>372684</v>
+        <v>372457</v>
       </c>
       <c r="R43" t="n">
-        <v>6934056</v>
+        <v>6934206</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4979,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122968318</v>
+        <v>122965816</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,34 +4995,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>372375</v>
+        <v>372684</v>
       </c>
       <c r="R44" t="n">
-        <v>6934215</v>
+        <v>6934056</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5081,10 +5081,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122967925</v>
+        <v>122967699</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,21 +5097,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>372457</v>
+        <v>372504</v>
       </c>
       <c r="R45" t="n">
-        <v>6934206</v>
+        <v>6934172</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,10 +5183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122967699</v>
+        <v>122961215</v>
       </c>
       <c r="B46" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,21 +5199,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>372504</v>
+        <v>372104</v>
       </c>
       <c r="R46" t="n">
-        <v>6934172</v>
+        <v>6934254</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122968251</v>
+        <v>122965016</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -5636,10 +5636,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>372404</v>
+        <v>372465</v>
       </c>
       <c r="R50" t="n">
-        <v>6934224</v>
+        <v>6934107</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5800,10 +5800,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122965016</v>
+        <v>122967574</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5816,37 +5816,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>372465</v>
+        <v>372536</v>
       </c>
       <c r="R52" t="n">
-        <v>6934107</v>
+        <v>6934127</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5902,10 +5907,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122967574</v>
+        <v>122967646</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5918,42 +5923,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>372536</v>
+        <v>372519</v>
       </c>
       <c r="R53" t="n">
-        <v>6934127</v>
+        <v>6934145</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122967646</v>
+        <v>122968251</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6045,14 +6045,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>372519</v>
+        <v>372404</v>
       </c>
       <c r="R54" t="n">
-        <v>6934145</v>
+        <v>6934224</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6417,7 +6417,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122969914</v>
+        <v>122969275</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -6453,14 +6453,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>372129</v>
+        <v>372204</v>
       </c>
       <c r="R58" t="n">
-        <v>6934375</v>
+        <v>6934300</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122969275</v>
+        <v>122968248</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>90940</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6535,34 +6535,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>372204</v>
+        <v>372404</v>
       </c>
       <c r="R59" t="n">
-        <v>6934300</v>
+        <v>6934224</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6621,10 +6621,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122968248</v>
+        <v>122968061</v>
       </c>
       <c r="B60" t="n">
-        <v>90940</v>
+        <v>82553</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6637,21 +6637,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>372404</v>
+        <v>372448</v>
       </c>
       <c r="R60" t="n">
-        <v>6934224</v>
+        <v>6934207</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,10 +6723,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122968061</v>
+        <v>122969914</v>
       </c>
       <c r="B61" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6739,21 +6739,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>372448</v>
+        <v>372129</v>
       </c>
       <c r="R61" t="n">
-        <v>6934207</v>
+        <v>6934375</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122970496</v>
+        <v>122968525</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372318</v>
+        <v>372330</v>
       </c>
       <c r="R2" t="n">
-        <v>6934300</v>
+        <v>6934242</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122962156</v>
+        <v>122969914</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372213</v>
+        <v>372129</v>
       </c>
       <c r="R3" t="n">
-        <v>6934190</v>
+        <v>6934375</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122968616</v>
+        <v>122965816</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372302</v>
+        <v>372684</v>
       </c>
       <c r="R4" t="n">
-        <v>6934249</v>
+        <v>6934056</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122960937</v>
+        <v>122965272</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372056</v>
+        <v>372519</v>
       </c>
       <c r="R6" t="n">
-        <v>6934270</v>
+        <v>6934058</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122961588</v>
+        <v>122964107</v>
       </c>
       <c r="B7" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372194</v>
+        <v>372305</v>
       </c>
       <c r="R7" t="n">
-        <v>6934243</v>
+        <v>6934147</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122968306</v>
+        <v>122965141</v>
       </c>
       <c r="B8" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372375</v>
+        <v>372528</v>
       </c>
       <c r="R8" t="n">
-        <v>6934215</v>
+        <v>6934080</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122965070</v>
+        <v>122968248</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>90940</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,42 +1512,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372491</v>
+        <v>372404</v>
       </c>
       <c r="R10" t="n">
-        <v>6934104</v>
+        <v>6934224</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122969456</v>
+        <v>122968318</v>
       </c>
       <c r="B11" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372175</v>
+        <v>372375</v>
       </c>
       <c r="R11" t="n">
-        <v>6934323</v>
+        <v>6934215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122968129</v>
+        <v>122970496</v>
       </c>
       <c r="B12" t="n">
-        <v>91632</v>
+        <v>90962</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,38 +1712,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372441</v>
+        <v>372318</v>
       </c>
       <c r="R12" t="n">
-        <v>6934188</v>
+        <v>6934300</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122970659</v>
+        <v>122965447</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,37 +1818,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372348</v>
+        <v>372613</v>
       </c>
       <c r="R13" t="n">
-        <v>6934275</v>
+        <v>6934029</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122965818</v>
+        <v>122969270</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372684</v>
+        <v>372204</v>
       </c>
       <c r="R14" t="n">
-        <v>6934056</v>
+        <v>6934300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122960569</v>
+        <v>122961461</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372015</v>
+        <v>372167</v>
       </c>
       <c r="R15" t="n">
-        <v>6934298</v>
+        <v>6934263</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122970155</v>
+        <v>122970193</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>90940</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372059</v>
+        <v>372119</v>
       </c>
       <c r="R16" t="n">
-        <v>6934345</v>
+        <v>6934355</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122962287</v>
+        <v>122967925</v>
       </c>
       <c r="B17" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>372237</v>
+        <v>372457</v>
       </c>
       <c r="R17" t="n">
-        <v>6934196</v>
+        <v>6934206</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122970193</v>
+        <v>122967646</v>
       </c>
       <c r="B18" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,34 +2333,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>372119</v>
+        <v>372519</v>
       </c>
       <c r="R18" t="n">
-        <v>6934355</v>
+        <v>6934145</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122963595</v>
+        <v>122969275</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2455,14 +2455,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>372223</v>
+        <v>372204</v>
       </c>
       <c r="R19" t="n">
-        <v>6934198</v>
+        <v>6934300</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122969270</v>
+        <v>122968966</v>
       </c>
       <c r="B20" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,34 +2537,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>372204</v>
+        <v>372261</v>
       </c>
       <c r="R20" t="n">
-        <v>6934300</v>
+        <v>6934264</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122963945</v>
+        <v>122965564</v>
       </c>
       <c r="B21" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,34 +2639,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>372274</v>
+        <v>372662</v>
       </c>
       <c r="R21" t="n">
-        <v>6934163</v>
+        <v>6934028</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122968525</v>
+        <v>122960569</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>372330</v>
+        <v>372015</v>
       </c>
       <c r="R22" t="n">
-        <v>6934242</v>
+        <v>6934298</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122969955</v>
+        <v>122968616</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,42 +2843,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>372131</v>
+        <v>372302</v>
       </c>
       <c r="R23" t="n">
-        <v>6934388</v>
+        <v>6934249</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2934,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122970713</v>
+        <v>122962156</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2950,42 +2945,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>372362</v>
+        <v>372213</v>
       </c>
       <c r="R24" t="n">
-        <v>6934267</v>
+        <v>6934190</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3041,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122961461</v>
+        <v>122965361</v>
       </c>
       <c r="B25" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,34 +3047,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>372167</v>
+        <v>372585</v>
       </c>
       <c r="R25" t="n">
-        <v>6934263</v>
+        <v>6934042</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122961144</v>
+        <v>122965818</v>
       </c>
       <c r="B26" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,34 +3149,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>372056</v>
+        <v>372684</v>
       </c>
       <c r="R26" t="n">
-        <v>6934270</v>
+        <v>6934056</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122963972</v>
+        <v>122968972</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3261,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3285,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>372274</v>
+        <v>372261</v>
       </c>
       <c r="R27" t="n">
-        <v>6934163</v>
+        <v>6934264</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122965907</v>
+        <v>122961588</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,34 +3353,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>372645</v>
+        <v>372194</v>
       </c>
       <c r="R28" t="n">
-        <v>6934077</v>
+        <v>6934243</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122965361</v>
+        <v>122963587</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,34 +3455,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>372585</v>
+        <v>372223</v>
       </c>
       <c r="R29" t="n">
-        <v>6934042</v>
+        <v>6934198</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122969101</v>
+        <v>122963945</v>
       </c>
       <c r="B30" t="n">
         <v>74863</v>
@@ -3591,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>372244</v>
+        <v>372274</v>
       </c>
       <c r="R30" t="n">
-        <v>6934274</v>
+        <v>6934163</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122969637</v>
+        <v>122962287</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3665,25 +3655,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3693,13 +3683,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>372139</v>
+        <v>372237</v>
       </c>
       <c r="R31" t="n">
-        <v>6934367</v>
+        <v>6934196</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3755,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122970500</v>
+        <v>122967699</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,34 +3761,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>372318</v>
+        <v>372504</v>
       </c>
       <c r="R32" t="n">
-        <v>6934300</v>
+        <v>6934172</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122968399</v>
+        <v>122970143</v>
       </c>
       <c r="B33" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,25 +3859,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3897,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>372360</v>
+        <v>372099</v>
       </c>
       <c r="R33" t="n">
-        <v>6934228</v>
+        <v>6934362</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3959,7 +3949,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122961601</v>
+        <v>122970500</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -3995,14 +3985,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>372194</v>
+        <v>372318</v>
       </c>
       <c r="R34" t="n">
-        <v>6934243</v>
+        <v>6934300</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122965141</v>
+        <v>122969456</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,34 +4067,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>372528</v>
+        <v>372175</v>
       </c>
       <c r="R35" t="n">
-        <v>6934080</v>
+        <v>6934323</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,7 +4153,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122967374</v>
+        <v>122970239</v>
       </c>
       <c r="B36" t="n">
         <v>74863</v>
@@ -4199,14 +4189,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>372563</v>
+        <v>372139</v>
       </c>
       <c r="R36" t="n">
-        <v>6934123</v>
+        <v>6934344</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122970143</v>
+        <v>122970638</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,37 +4271,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>372099</v>
+        <v>372342</v>
       </c>
       <c r="R37" t="n">
-        <v>6934362</v>
+        <v>6934292</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4367,10 +4362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122968972</v>
+        <v>122968129</v>
       </c>
       <c r="B38" t="n">
-        <v>74863</v>
+        <v>91632</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4379,25 +4374,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,10 +4402,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>372261</v>
+        <v>372441</v>
       </c>
       <c r="R38" t="n">
-        <v>6934264</v>
+        <v>6934188</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,10 +4464,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122968966</v>
+        <v>122967390</v>
       </c>
       <c r="B39" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4485,34 +4480,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>372261</v>
+        <v>372563</v>
       </c>
       <c r="R39" t="n">
-        <v>6934264</v>
+        <v>6934123</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,10 +4566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122961339</v>
+        <v>122968312</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,21 +4582,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>372139</v>
+        <v>372375</v>
       </c>
       <c r="R40" t="n">
-        <v>6934261</v>
+        <v>6934215</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,10 +4668,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122965746</v>
+        <v>122965016</v>
       </c>
       <c r="B41" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,34 +4684,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>372716</v>
+        <v>372465</v>
       </c>
       <c r="R41" t="n">
-        <v>6934036</v>
+        <v>6934107</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4775,10 +4770,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122968318</v>
+        <v>122968399</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4787,25 +4782,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4815,10 +4810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>372375</v>
+        <v>372360</v>
       </c>
       <c r="R42" t="n">
-        <v>6934215</v>
+        <v>6934228</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4877,7 +4872,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122967925</v>
+        <v>122961601</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -4917,10 +4912,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>372457</v>
+        <v>372194</v>
       </c>
       <c r="R43" t="n">
-        <v>6934206</v>
+        <v>6934243</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4979,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122965816</v>
+        <v>122961215</v>
       </c>
       <c r="B44" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,34 +4990,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>372684</v>
+        <v>372104</v>
       </c>
       <c r="R44" t="n">
-        <v>6934056</v>
+        <v>6934254</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5081,10 +5076,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122967699</v>
+        <v>122969101</v>
       </c>
       <c r="B45" t="n">
-        <v>90962</v>
+        <v>74863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,21 +5092,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5121,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>372504</v>
+        <v>372244</v>
       </c>
       <c r="R45" t="n">
-        <v>6934172</v>
+        <v>6934274</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122961215</v>
+        <v>122968171</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,21 +5194,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5223,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>372104</v>
+        <v>372420</v>
       </c>
       <c r="R46" t="n">
-        <v>6934254</v>
+        <v>6934199</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5285,7 +5280,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122963587</v>
+        <v>122964992</v>
       </c>
       <c r="B47" t="n">
         <v>74863</v>
@@ -5325,10 +5320,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>372223</v>
+        <v>372465</v>
       </c>
       <c r="R47" t="n">
-        <v>6934198</v>
+        <v>6934107</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5387,7 +5382,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122965447</v>
+        <v>122969955</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -5428,14 +5423,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>372613</v>
+        <v>372131</v>
       </c>
       <c r="R48" t="n">
-        <v>6934029</v>
+        <v>6934388</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5494,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122966267</v>
+        <v>122970713</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5510,37 +5505,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>372606</v>
+        <v>372362</v>
       </c>
       <c r="R49" t="n">
-        <v>6934099</v>
+        <v>6934267</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122965016</v>
+        <v>122968061</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5612,21 +5612,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5636,10 +5636,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>372465</v>
+        <v>372448</v>
       </c>
       <c r="R50" t="n">
-        <v>6934107</v>
+        <v>6934207</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122964107</v>
+        <v>122969637</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -5738,10 +5738,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>372305</v>
+        <v>372139</v>
       </c>
       <c r="R51" t="n">
-        <v>6934147</v>
+        <v>6934367</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5800,10 +5800,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122967574</v>
+        <v>122963972</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5816,42 +5816,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>372536</v>
+        <v>372274</v>
       </c>
       <c r="R52" t="n">
-        <v>6934127</v>
+        <v>6934163</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5907,7 +5902,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122967646</v>
+        <v>122963595</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -5943,14 +5938,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>372519</v>
+        <v>372223</v>
       </c>
       <c r="R53" t="n">
-        <v>6934145</v>
+        <v>6934198</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6009,7 +6004,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122968251</v>
+        <v>122960937</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6049,10 +6044,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>372404</v>
+        <v>372056</v>
       </c>
       <c r="R54" t="n">
-        <v>6934224</v>
+        <v>6934270</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6111,10 +6106,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122968171</v>
+        <v>122970659</v>
       </c>
       <c r="B55" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6127,34 +6122,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>372420</v>
+        <v>372348</v>
       </c>
       <c r="R55" t="n">
-        <v>6934199</v>
+        <v>6934275</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6213,10 +6208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122964992</v>
+        <v>122965907</v>
       </c>
       <c r="B56" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6229,34 +6224,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>372465</v>
+        <v>372645</v>
       </c>
       <c r="R56" t="n">
-        <v>6934107</v>
+        <v>6934077</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6315,10 +6310,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122965564</v>
+        <v>122969444</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6331,34 +6326,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>372662</v>
+        <v>372175</v>
       </c>
       <c r="R57" t="n">
-        <v>6934028</v>
+        <v>6934323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6417,7 +6412,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122969275</v>
+        <v>122970155</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -6453,14 +6448,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>372204</v>
+        <v>372059</v>
       </c>
       <c r="R58" t="n">
-        <v>6934300</v>
+        <v>6934345</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,10 +6514,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122968248</v>
+        <v>122961144</v>
       </c>
       <c r="B59" t="n">
-        <v>90940</v>
+        <v>74863</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6535,21 +6530,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6559,10 +6554,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>372404</v>
+        <v>372056</v>
       </c>
       <c r="R59" t="n">
-        <v>6934224</v>
+        <v>6934270</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6621,10 +6616,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122968061</v>
+        <v>122966267</v>
       </c>
       <c r="B60" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6637,34 +6632,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>372448</v>
+        <v>372606</v>
       </c>
       <c r="R60" t="n">
-        <v>6934207</v>
+        <v>6934099</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,10 +6718,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122969914</v>
+        <v>122967374</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6739,34 +6734,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>372129</v>
+        <v>372563</v>
       </c>
       <c r="R61" t="n">
-        <v>6934375</v>
+        <v>6934123</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6927,10 +6922,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122970239</v>
+        <v>122967574</v>
       </c>
       <c r="B63" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6943,37 +6938,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>372139</v>
+        <v>372536</v>
       </c>
       <c r="R63" t="n">
-        <v>6934344</v>
+        <v>6934127</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122970638</v>
+        <v>122968251</v>
       </c>
       <c r="B64" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7045,42 +7045,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>372342</v>
+        <v>372404</v>
       </c>
       <c r="R64" t="n">
-        <v>6934292</v>
+        <v>6934224</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7136,7 +7131,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122965272</v>
+        <v>122965746</v>
       </c>
       <c r="B65" t="n">
         <v>74863</v>
@@ -7176,10 +7171,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>372519</v>
+        <v>372716</v>
       </c>
       <c r="R65" t="n">
-        <v>6934058</v>
+        <v>6934036</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7233,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122967390</v>
+        <v>122965070</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7254,37 +7249,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>372563</v>
+        <v>372491</v>
       </c>
       <c r="R66" t="n">
-        <v>6934123</v>
+        <v>6934104</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122969444</v>
+        <v>122961339</v>
       </c>
       <c r="B67" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7356,21 +7356,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>372175</v>
+        <v>372139</v>
       </c>
       <c r="R67" t="n">
-        <v>6934323</v>
+        <v>6934261</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122968312</v>
+        <v>122968306</v>
       </c>
       <c r="B68" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7458,21 +7458,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122968248</v>
+        <v>122965447</v>
       </c>
       <c r="B10" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,37 +1512,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372404</v>
+        <v>372613</v>
       </c>
       <c r="R10" t="n">
-        <v>6934224</v>
+        <v>6934029</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122968318</v>
+        <v>122968248</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>90940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372375</v>
+        <v>372404</v>
       </c>
       <c r="R11" t="n">
-        <v>6934215</v>
+        <v>6934224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122970496</v>
+        <v>122968318</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,34 +1721,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372318</v>
+        <v>372375</v>
       </c>
       <c r="R12" t="n">
-        <v>6934300</v>
+        <v>6934215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122965447</v>
+        <v>122970496</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,42 +1823,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372613</v>
+        <v>372318</v>
       </c>
       <c r="R13" t="n">
-        <v>6934029</v>
+        <v>6934300</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122970193</v>
+        <v>122967925</v>
       </c>
       <c r="B16" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372119</v>
+        <v>372457</v>
       </c>
       <c r="R16" t="n">
-        <v>6934355</v>
+        <v>6934206</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122967925</v>
+        <v>122970193</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>90940</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>372457</v>
+        <v>372119</v>
       </c>
       <c r="R17" t="n">
-        <v>6934206</v>
+        <v>6934355</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122968251</v>
+        <v>122965070</v>
       </c>
       <c r="B64" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7045,37 +7045,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>372404</v>
+        <v>372491</v>
       </c>
       <c r="R64" t="n">
-        <v>6934224</v>
+        <v>6934104</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7131,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122965746</v>
+        <v>122961339</v>
       </c>
       <c r="B65" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7147,34 +7152,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>372716</v>
+        <v>372139</v>
       </c>
       <c r="R65" t="n">
-        <v>6934036</v>
+        <v>6934261</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7233,10 +7238,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122965070</v>
+        <v>122968306</v>
       </c>
       <c r="B66" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7249,42 +7254,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>372491</v>
+        <v>372375</v>
       </c>
       <c r="R66" t="n">
-        <v>6934104</v>
+        <v>6934215</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122961339</v>
+        <v>122968251</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>372139</v>
+        <v>372404</v>
       </c>
       <c r="R67" t="n">
-        <v>6934261</v>
+        <v>6934224</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122968306</v>
+        <v>122965746</v>
       </c>
       <c r="B68" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7458,34 +7458,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>372375</v>
+        <v>372716</v>
       </c>
       <c r="R68" t="n">
-        <v>6934215</v>
+        <v>6934036</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122965816</v>
+        <v>122965141</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372684</v>
+        <v>372528</v>
       </c>
       <c r="R4" t="n">
-        <v>6934056</v>
+        <v>6934080</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122969120</v>
+        <v>122961738</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,37 +997,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372226</v>
+        <v>372193</v>
       </c>
       <c r="R5" t="n">
-        <v>6934263</v>
+        <v>6934231</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122965272</v>
+        <v>122965816</v>
       </c>
       <c r="B6" t="n">
         <v>74863</v>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372519</v>
+        <v>372684</v>
       </c>
       <c r="R6" t="n">
-        <v>6934058</v>
+        <v>6934056</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122964107</v>
+        <v>122969120</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372305</v>
+        <v>372226</v>
       </c>
       <c r="R7" t="n">
-        <v>6934147</v>
+        <v>6934263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122965141</v>
+        <v>122965272</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372528</v>
+        <v>372519</v>
       </c>
       <c r="R8" t="n">
-        <v>6934080</v>
+        <v>6934058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122961738</v>
+        <v>122964107</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,42 +1410,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372193</v>
+        <v>372305</v>
       </c>
       <c r="R9" t="n">
-        <v>6934231</v>
+        <v>6934147</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122961588</v>
+        <v>122963587</v>
       </c>
       <c r="B28" t="n">
-        <v>90944</v>
+        <v>74863</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>372194</v>
+        <v>372223</v>
       </c>
       <c r="R28" t="n">
-        <v>6934243</v>
+        <v>6934198</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122963587</v>
+        <v>122963945</v>
       </c>
       <c r="B29" t="n">
         <v>74863</v>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>372223</v>
+        <v>372274</v>
       </c>
       <c r="R29" t="n">
-        <v>6934198</v>
+        <v>6934163</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122963945</v>
+        <v>122962287</v>
       </c>
       <c r="B30" t="n">
-        <v>74863</v>
+        <v>57589</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3553,25 +3553,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,13 +3581,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>372274</v>
+        <v>372237</v>
       </c>
       <c r="R30" t="n">
-        <v>6934163</v>
+        <v>6934196</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122962287</v>
+        <v>122961588</v>
       </c>
       <c r="B31" t="n">
-        <v>57589</v>
+        <v>90944</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3655,25 +3655,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,13 +3683,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>372237</v>
+        <v>372194</v>
       </c>
       <c r="R31" t="n">
-        <v>6934196</v>
+        <v>6934243</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122968525</v>
+        <v>122967699</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372330</v>
+        <v>372504</v>
       </c>
       <c r="R2" t="n">
-        <v>6934242</v>
+        <v>6934172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122969914</v>
+        <v>122961601</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372129</v>
+        <v>372194</v>
       </c>
       <c r="R3" t="n">
-        <v>6934375</v>
+        <v>6934243</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122965141</v>
+        <v>122970638</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372528</v>
+        <v>372342</v>
       </c>
       <c r="R4" t="n">
-        <v>6934080</v>
+        <v>6934292</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122961738</v>
+        <v>122968399</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,46 +998,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372193</v>
+        <v>372360</v>
       </c>
       <c r="R5" t="n">
-        <v>6934231</v>
+        <v>6934228</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122965816</v>
+        <v>122961738</v>
       </c>
       <c r="B6" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,37 +1104,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372684</v>
+        <v>372193</v>
       </c>
       <c r="R6" t="n">
-        <v>6934056</v>
+        <v>6934231</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122969120</v>
+        <v>122968251</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372226</v>
+        <v>372404</v>
       </c>
       <c r="R7" t="n">
-        <v>6934263</v>
+        <v>6934224</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122965272</v>
+        <v>122967646</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,7 +1340,7 @@
         <v>372519</v>
       </c>
       <c r="R8" t="n">
-        <v>6934058</v>
+        <v>6934145</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122964107</v>
+        <v>122961215</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372305</v>
+        <v>372104</v>
       </c>
       <c r="R9" t="n">
-        <v>6934147</v>
+        <v>6934254</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122965447</v>
+        <v>122968306</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,42 +1517,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372613</v>
+        <v>372375</v>
       </c>
       <c r="R10" t="n">
-        <v>6934029</v>
+        <v>6934215</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122968248</v>
+        <v>122965016</v>
       </c>
       <c r="B11" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372404</v>
+        <v>372465</v>
       </c>
       <c r="R11" t="n">
-        <v>6934224</v>
+        <v>6934107</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122968318</v>
+        <v>122968129</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>91640</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372375</v>
+        <v>372441</v>
       </c>
       <c r="R12" t="n">
-        <v>6934215</v>
+        <v>6934188</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122970496</v>
+        <v>122964107</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,34 +1823,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372318</v>
+        <v>372305</v>
       </c>
       <c r="R13" t="n">
-        <v>6934300</v>
+        <v>6934147</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122969270</v>
+        <v>122967390</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372204</v>
+        <v>372563</v>
       </c>
       <c r="R14" t="n">
-        <v>6934300</v>
+        <v>6934123</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122961461</v>
+        <v>122970193</v>
       </c>
       <c r="B15" t="n">
-        <v>74863</v>
+        <v>90948</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372167</v>
+        <v>372119</v>
       </c>
       <c r="R15" t="n">
-        <v>6934263</v>
+        <v>6934355</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122967925</v>
+        <v>122965746</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372457</v>
+        <v>372716</v>
       </c>
       <c r="R16" t="n">
-        <v>6934206</v>
+        <v>6934036</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122970193</v>
+        <v>122961461</v>
       </c>
       <c r="B17" t="n">
-        <v>90940</v>
+        <v>74863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>372119</v>
+        <v>372167</v>
       </c>
       <c r="R17" t="n">
-        <v>6934355</v>
+        <v>6934263</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122967646</v>
+        <v>122965272</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
         <v>372519</v>
       </c>
       <c r="R18" t="n">
-        <v>6934145</v>
+        <v>6934058</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122969275</v>
+        <v>122968061</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,34 +2435,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>372204</v>
+        <v>372448</v>
       </c>
       <c r="R19" t="n">
-        <v>6934300</v>
+        <v>6934207</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122968966</v>
+        <v>122965447</v>
       </c>
       <c r="B20" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,37 +2537,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>372261</v>
+        <v>372613</v>
       </c>
       <c r="R20" t="n">
-        <v>6934264</v>
+        <v>6934029</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2623,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122965564</v>
+        <v>122961588</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,34 +2644,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>372662</v>
+        <v>372194</v>
       </c>
       <c r="R21" t="n">
-        <v>6934028</v>
+        <v>6934243</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122960569</v>
+        <v>122965141</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2761,14 +2766,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>372015</v>
+        <v>372528</v>
       </c>
       <c r="R22" t="n">
-        <v>6934298</v>
+        <v>6934080</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2832,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122968616</v>
+        <v>122965818</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2863,14 +2868,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>372302</v>
+        <v>372684</v>
       </c>
       <c r="R23" t="n">
-        <v>6934249</v>
+        <v>6934056</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122962156</v>
+        <v>122969120</v>
       </c>
       <c r="B24" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,21 +2950,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>372213</v>
+        <v>372226</v>
       </c>
       <c r="R24" t="n">
-        <v>6934190</v>
+        <v>6934263</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122965361</v>
+        <v>122961144</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,34 +3052,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>372585</v>
+        <v>372056</v>
       </c>
       <c r="R25" t="n">
-        <v>6934042</v>
+        <v>6934270</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3138,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122965818</v>
+        <v>122964992</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,34 +3154,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>372684</v>
+        <v>372465</v>
       </c>
       <c r="R26" t="n">
-        <v>6934056</v>
+        <v>6934107</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122968972</v>
+        <v>122970496</v>
       </c>
       <c r="B27" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,34 +3256,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>372261</v>
+        <v>372318</v>
       </c>
       <c r="R27" t="n">
-        <v>6934264</v>
+        <v>6934300</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,7 +3342,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122963587</v>
+        <v>122970239</v>
       </c>
       <c r="B28" t="n">
         <v>74863</v>
@@ -3377,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>372223</v>
+        <v>372139</v>
       </c>
       <c r="R28" t="n">
-        <v>6934198</v>
+        <v>6934344</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,7 +3444,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122963945</v>
+        <v>122968171</v>
       </c>
       <c r="B29" t="n">
         <v>74863</v>
@@ -3479,10 +3484,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>372274</v>
+        <v>372420</v>
       </c>
       <c r="R29" t="n">
-        <v>6934163</v>
+        <v>6934199</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3546,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122962287</v>
+        <v>122963945</v>
       </c>
       <c r="B30" t="n">
-        <v>57589</v>
+        <v>74863</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3553,25 +3558,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,13 +3586,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>372237</v>
+        <v>372274</v>
       </c>
       <c r="R30" t="n">
-        <v>6934196</v>
+        <v>6934163</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3643,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122961588</v>
+        <v>122969955</v>
       </c>
       <c r="B31" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,37 +3664,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>372194</v>
+        <v>372131</v>
       </c>
       <c r="R31" t="n">
-        <v>6934243</v>
+        <v>6934388</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3745,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122967699</v>
+        <v>122968248</v>
       </c>
       <c r="B32" t="n">
-        <v>90962</v>
+        <v>90948</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3771,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>372504</v>
+        <v>372404</v>
       </c>
       <c r="R32" t="n">
-        <v>6934172</v>
+        <v>6934224</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,7 +3857,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122970143</v>
+        <v>122965361</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -3883,14 +3893,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>372099</v>
+        <v>372585</v>
       </c>
       <c r="R33" t="n">
-        <v>6934362</v>
+        <v>6934042</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,7 +3959,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122970500</v>
+        <v>122968525</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -3985,14 +3995,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>372318</v>
+        <v>372330</v>
       </c>
       <c r="R34" t="n">
-        <v>6934300</v>
+        <v>6934242</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,10 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122969456</v>
+        <v>122965907</v>
       </c>
       <c r="B35" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4067,34 +4077,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>372175</v>
+        <v>372645</v>
       </c>
       <c r="R35" t="n">
-        <v>6934323</v>
+        <v>6934077</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122970239</v>
+        <v>122968966</v>
       </c>
       <c r="B36" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4169,21 +4179,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4193,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>372139</v>
+        <v>372261</v>
       </c>
       <c r="R36" t="n">
-        <v>6934344</v>
+        <v>6934264</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122970638</v>
+        <v>122967374</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4271,42 +4281,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>372342</v>
+        <v>372563</v>
       </c>
       <c r="R37" t="n">
-        <v>6934292</v>
+        <v>6934123</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4362,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122968129</v>
+        <v>122968972</v>
       </c>
       <c r="B38" t="n">
-        <v>91632</v>
+        <v>74863</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4374,25 +4379,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4402,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>372441</v>
+        <v>372261</v>
       </c>
       <c r="R38" t="n">
-        <v>6934188</v>
+        <v>6934264</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4464,7 +4469,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122967390</v>
+        <v>122970155</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4500,14 +4505,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>372563</v>
+        <v>372059</v>
       </c>
       <c r="R39" t="n">
-        <v>6934123</v>
+        <v>6934345</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122968312</v>
+        <v>122963972</v>
       </c>
       <c r="B40" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4582,21 +4587,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>372375</v>
+        <v>372274</v>
       </c>
       <c r="R40" t="n">
-        <v>6934215</v>
+        <v>6934163</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4668,7 +4673,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122965016</v>
+        <v>122970659</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4704,14 +4709,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>372465</v>
+        <v>372348</v>
       </c>
       <c r="R41" t="n">
-        <v>6934107</v>
+        <v>6934275</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,10 +4775,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122968399</v>
+        <v>122965070</v>
       </c>
       <c r="B42" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4782,41 +4787,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>372360</v>
+        <v>372491</v>
       </c>
       <c r="R42" t="n">
-        <v>6934228</v>
+        <v>6934104</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4872,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122961601</v>
+        <v>122967925</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -4912,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>372194</v>
+        <v>372457</v>
       </c>
       <c r="R43" t="n">
-        <v>6934243</v>
+        <v>6934206</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,7 +4984,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122961215</v>
+        <v>122969914</v>
       </c>
       <c r="B44" t="n">
         <v>78766</v>
@@ -5014,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>372104</v>
+        <v>372129</v>
       </c>
       <c r="R44" t="n">
-        <v>6934254</v>
+        <v>6934375</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5076,10 +5086,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122969101</v>
+        <v>122963595</v>
       </c>
       <c r="B45" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5092,21 +5102,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5116,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>372244</v>
+        <v>372223</v>
       </c>
       <c r="R45" t="n">
-        <v>6934274</v>
+        <v>6934198</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5178,7 +5188,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122968171</v>
+        <v>122968312</v>
       </c>
       <c r="B46" t="n">
         <v>74863</v>
@@ -5218,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>372420</v>
+        <v>372375</v>
       </c>
       <c r="R46" t="n">
-        <v>6934199</v>
+        <v>6934215</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5280,10 +5290,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122964992</v>
+        <v>122966267</v>
       </c>
       <c r="B47" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5296,34 +5306,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>372465</v>
+        <v>372606</v>
       </c>
       <c r="R47" t="n">
-        <v>6934107</v>
+        <v>6934099</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5382,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122969955</v>
+        <v>122969637</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5398,42 +5408,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>372131</v>
+        <v>372139</v>
       </c>
       <c r="R48" t="n">
-        <v>6934388</v>
+        <v>6934367</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5489,10 +5494,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122970713</v>
+        <v>122970143</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,42 +5510,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>372362</v>
+        <v>372099</v>
       </c>
       <c r="R49" t="n">
-        <v>6934267</v>
+        <v>6934362</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122968061</v>
+        <v>122960569</v>
       </c>
       <c r="B50" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5612,21 +5612,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5636,10 +5636,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>372448</v>
+        <v>372015</v>
       </c>
       <c r="R50" t="n">
-        <v>6934207</v>
+        <v>6934298</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122969637</v>
+        <v>122965564</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -5734,14 +5734,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>372139</v>
+        <v>372662</v>
       </c>
       <c r="R51" t="n">
-        <v>6934367</v>
+        <v>6934028</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5800,10 +5800,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122963972</v>
+        <v>122969456</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5816,21 +5816,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5840,10 +5840,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>372274</v>
+        <v>372175</v>
       </c>
       <c r="R52" t="n">
-        <v>6934163</v>
+        <v>6934323</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5902,7 +5902,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122963595</v>
+        <v>122968616</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>372223</v>
+        <v>372302</v>
       </c>
       <c r="R53" t="n">
-        <v>6934198</v>
+        <v>6934249</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122960937</v>
+        <v>122969444</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6020,21 +6020,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6044,10 +6044,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>372056</v>
+        <v>372175</v>
       </c>
       <c r="R54" t="n">
-        <v>6934270</v>
+        <v>6934323</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6106,10 +6106,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122970659</v>
+        <v>122967574</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6122,37 +6122,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>372348</v>
+        <v>372536</v>
       </c>
       <c r="R55" t="n">
-        <v>6934275</v>
+        <v>6934127</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6208,10 +6213,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122965907</v>
+        <v>122970713</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6224,37 +6229,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>372645</v>
+        <v>372362</v>
       </c>
       <c r="R56" t="n">
-        <v>6934077</v>
+        <v>6934267</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6310,10 +6320,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122969444</v>
+        <v>122962287</v>
       </c>
       <c r="B57" t="n">
-        <v>90962</v>
+        <v>57589</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6322,25 +6332,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6350,13 +6360,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>372175</v>
+        <v>372237</v>
       </c>
       <c r="R57" t="n">
-        <v>6934323</v>
+        <v>6934196</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6412,7 +6422,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122970155</v>
+        <v>122961339</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -6452,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>372059</v>
+        <v>372139</v>
       </c>
       <c r="R58" t="n">
-        <v>6934345</v>
+        <v>6934261</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6514,10 +6524,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122961144</v>
+        <v>122969270</v>
       </c>
       <c r="B59" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6530,34 +6540,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>372056</v>
+        <v>372204</v>
       </c>
       <c r="R59" t="n">
-        <v>6934270</v>
+        <v>6934300</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6616,10 +6626,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122966267</v>
+        <v>122965816</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6632,21 +6642,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6656,10 +6666,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>372606</v>
+        <v>372684</v>
       </c>
       <c r="R60" t="n">
-        <v>6934099</v>
+        <v>6934056</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6718,10 +6728,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122967374</v>
+        <v>122968318</v>
       </c>
       <c r="B61" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6734,34 +6744,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>372563</v>
+        <v>372375</v>
       </c>
       <c r="R61" t="n">
-        <v>6934123</v>
+        <v>6934215</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6820,7 +6830,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122970429</v>
+        <v>122969275</v>
       </c>
       <c r="B62" t="n">
         <v>78766</v>
@@ -6856,14 +6866,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>372253</v>
+        <v>372204</v>
       </c>
       <c r="R62" t="n">
-        <v>6934293</v>
+        <v>6934300</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6922,10 +6932,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122967574</v>
+        <v>122970429</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6938,42 +6948,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>372536</v>
+        <v>372253</v>
       </c>
       <c r="R63" t="n">
-        <v>6934127</v>
+        <v>6934293</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7029,10 +7034,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122965070</v>
+        <v>122970500</v>
       </c>
       <c r="B64" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7045,42 +7050,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>372491</v>
+        <v>372318</v>
       </c>
       <c r="R64" t="n">
-        <v>6934104</v>
+        <v>6934300</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122961339</v>
+        <v>122963587</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>372139</v>
+        <v>372223</v>
       </c>
       <c r="R65" t="n">
-        <v>6934261</v>
+        <v>6934198</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122968306</v>
+        <v>122960937</v>
       </c>
       <c r="B66" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7254,21 +7254,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>372375</v>
+        <v>372056</v>
       </c>
       <c r="R66" t="n">
-        <v>6934215</v>
+        <v>6934270</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122968251</v>
+        <v>122962156</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7356,21 +7356,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>372404</v>
+        <v>372213</v>
       </c>
       <c r="R67" t="n">
-        <v>6934224</v>
+        <v>6934190</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,7 +7442,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122965746</v>
+        <v>122969101</v>
       </c>
       <c r="B68" t="n">
         <v>74863</v>
@@ -7478,14 +7478,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>372716</v>
+        <v>372244</v>
       </c>
       <c r="R68" t="n">
-        <v>6934036</v>
+        <v>6934274</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122967699</v>
+        <v>122970638</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372504</v>
+        <v>372342</v>
       </c>
       <c r="R2" t="n">
-        <v>6934172</v>
+        <v>6934292</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122961601</v>
+        <v>122967699</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372194</v>
+        <v>372504</v>
       </c>
       <c r="R3" t="n">
-        <v>6934243</v>
+        <v>6934172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122970638</v>
+        <v>122961601</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,42 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372342</v>
+        <v>372194</v>
       </c>
       <c r="R4" t="n">
-        <v>6934292</v>
+        <v>6934243</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122970638</v>
+        <v>122963972</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372342</v>
+        <v>372274</v>
       </c>
       <c r="R2" t="n">
-        <v>6934292</v>
+        <v>6934163</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122967699</v>
+        <v>122965272</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372504</v>
+        <v>372519</v>
       </c>
       <c r="R3" t="n">
-        <v>6934172</v>
+        <v>6934058</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122961601</v>
+        <v>122968525</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372194</v>
+        <v>372330</v>
       </c>
       <c r="R4" t="n">
-        <v>6934243</v>
+        <v>6934242</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122968399</v>
+        <v>122964992</v>
       </c>
       <c r="B5" t="n">
-        <v>79876</v>
+        <v>74863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372360</v>
+        <v>372465</v>
       </c>
       <c r="R5" t="n">
-        <v>6934228</v>
+        <v>6934107</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122961738</v>
+        <v>122965907</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,42 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372193</v>
+        <v>372645</v>
       </c>
       <c r="R6" t="n">
-        <v>6934231</v>
+        <v>6934077</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122968251</v>
+        <v>122962287</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372404</v>
+        <v>372237</v>
       </c>
       <c r="R7" t="n">
-        <v>6934224</v>
+        <v>6934196</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122967646</v>
+        <v>122965564</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1337,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372519</v>
+        <v>372662</v>
       </c>
       <c r="R8" t="n">
-        <v>6934145</v>
+        <v>6934028</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122961215</v>
+        <v>122963587</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372104</v>
+        <v>372223</v>
       </c>
       <c r="R9" t="n">
-        <v>6934254</v>
+        <v>6934198</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122968306</v>
+        <v>122961601</v>
       </c>
       <c r="B10" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372375</v>
+        <v>372194</v>
       </c>
       <c r="R10" t="n">
-        <v>6934215</v>
+        <v>6934243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122965016</v>
+        <v>122961339</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372465</v>
+        <v>372139</v>
       </c>
       <c r="R11" t="n">
-        <v>6934107</v>
+        <v>6934261</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122968129</v>
+        <v>122961461</v>
       </c>
       <c r="B12" t="n">
-        <v>91640</v>
+        <v>74863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372441</v>
+        <v>372167</v>
       </c>
       <c r="R12" t="n">
-        <v>6934188</v>
+        <v>6934263</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122964107</v>
+        <v>122969444</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372305</v>
+        <v>372175</v>
       </c>
       <c r="R13" t="n">
-        <v>6934147</v>
+        <v>6934323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122967390</v>
+        <v>122961588</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,34 +1915,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372563</v>
+        <v>372194</v>
       </c>
       <c r="R14" t="n">
-        <v>6934123</v>
+        <v>6934243</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122970193</v>
+        <v>122968306</v>
       </c>
       <c r="B15" t="n">
-        <v>90948</v>
+        <v>82553</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372119</v>
+        <v>372375</v>
       </c>
       <c r="R15" t="n">
-        <v>6934355</v>
+        <v>6934215</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122965746</v>
+        <v>122968251</v>
       </c>
       <c r="B16" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,34 +2119,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372716</v>
+        <v>372404</v>
       </c>
       <c r="R16" t="n">
-        <v>6934036</v>
+        <v>6934224</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122961461</v>
+        <v>122965818</v>
       </c>
       <c r="B17" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,34 +2221,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>372167</v>
+        <v>372684</v>
       </c>
       <c r="R17" t="n">
-        <v>6934263</v>
+        <v>6934056</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122965272</v>
+        <v>122970143</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,34 +2323,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>372519</v>
+        <v>372099</v>
       </c>
       <c r="R18" t="n">
-        <v>6934058</v>
+        <v>6934362</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122968061</v>
+        <v>122963945</v>
       </c>
       <c r="B19" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>372448</v>
+        <v>372274</v>
       </c>
       <c r="R19" t="n">
-        <v>6934207</v>
+        <v>6934163</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122965447</v>
+        <v>122970638</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2557,7 +2547,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2566,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>372613</v>
+        <v>372342</v>
       </c>
       <c r="R20" t="n">
-        <v>6934029</v>
+        <v>6934292</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2628,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122961588</v>
+        <v>122969120</v>
       </c>
       <c r="B21" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>372194</v>
+        <v>372226</v>
       </c>
       <c r="R21" t="n">
-        <v>6934243</v>
+        <v>6934263</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122965141</v>
+        <v>122970659</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2770,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>372528</v>
+        <v>372348</v>
       </c>
       <c r="R22" t="n">
-        <v>6934080</v>
+        <v>6934275</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2822,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122965818</v>
+        <v>122963595</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2868,14 +2858,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>372684</v>
+        <v>372223</v>
       </c>
       <c r="R23" t="n">
-        <v>6934056</v>
+        <v>6934198</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122969120</v>
+        <v>122970496</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2950,34 +2940,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>372226</v>
+        <v>372318</v>
       </c>
       <c r="R24" t="n">
-        <v>6934263</v>
+        <v>6934300</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122961144</v>
+        <v>122970193</v>
       </c>
       <c r="B25" t="n">
-        <v>74863</v>
+        <v>90948</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3052,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3076,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>372056</v>
+        <v>372119</v>
       </c>
       <c r="R25" t="n">
-        <v>6934270</v>
+        <v>6934355</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122964992</v>
+        <v>122965447</v>
       </c>
       <c r="B26" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3154,37 +3144,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>372465</v>
+        <v>372613</v>
       </c>
       <c r="R26" t="n">
-        <v>6934107</v>
+        <v>6934029</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3240,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122970496</v>
+        <v>122969456</v>
       </c>
       <c r="B27" t="n">
-        <v>90970</v>
+        <v>74863</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3256,34 +3251,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>372318</v>
+        <v>372175</v>
       </c>
       <c r="R27" t="n">
-        <v>6934300</v>
+        <v>6934323</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,7 +3337,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122970239</v>
+        <v>122961144</v>
       </c>
       <c r="B28" t="n">
         <v>74863</v>
@@ -3382,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>372139</v>
+        <v>372056</v>
       </c>
       <c r="R28" t="n">
-        <v>6934344</v>
+        <v>6934270</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,7 +3439,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122968171</v>
+        <v>122969101</v>
       </c>
       <c r="B29" t="n">
         <v>74863</v>
@@ -3484,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>372420</v>
+        <v>372244</v>
       </c>
       <c r="R29" t="n">
-        <v>6934199</v>
+        <v>6934274</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3546,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122963945</v>
+        <v>122967374</v>
       </c>
       <c r="B30" t="n">
         <v>74863</v>
@@ -3582,14 +3577,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>372274</v>
+        <v>372563</v>
       </c>
       <c r="R30" t="n">
-        <v>6934163</v>
+        <v>6934123</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122969955</v>
+        <v>122968129</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>91640</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3660,46 +3655,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>372131</v>
+        <v>372441</v>
       </c>
       <c r="R31" t="n">
-        <v>6934388</v>
+        <v>6934188</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3755,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122968248</v>
+        <v>122968061</v>
       </c>
       <c r="B32" t="n">
-        <v>90948</v>
+        <v>82553</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3795,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>372404</v>
+        <v>372448</v>
       </c>
       <c r="R32" t="n">
-        <v>6934224</v>
+        <v>6934207</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,7 +3847,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122965361</v>
+        <v>122960569</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -3893,14 +3883,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>372585</v>
+        <v>372015</v>
       </c>
       <c r="R33" t="n">
-        <v>6934042</v>
+        <v>6934298</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3959,7 +3949,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122968525</v>
+        <v>122968616</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -3999,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>372330</v>
+        <v>372302</v>
       </c>
       <c r="R34" t="n">
-        <v>6934242</v>
+        <v>6934249</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122965907</v>
+        <v>122967574</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,37 +4067,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>372645</v>
+        <v>372536</v>
       </c>
       <c r="R35" t="n">
-        <v>6934077</v>
+        <v>6934127</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4163,10 +4158,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122968966</v>
+        <v>122969270</v>
       </c>
       <c r="B36" t="n">
-        <v>82553</v>
+        <v>90970</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,34 +4174,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>372261</v>
+        <v>372204</v>
       </c>
       <c r="R36" t="n">
-        <v>6934264</v>
+        <v>6934300</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,7 +4260,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122967374</v>
+        <v>122970239</v>
       </c>
       <c r="B37" t="n">
         <v>74863</v>
@@ -4301,14 +4296,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>372563</v>
+        <v>372139</v>
       </c>
       <c r="R37" t="n">
-        <v>6934123</v>
+        <v>6934344</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,7 +4362,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122968972</v>
+        <v>122968312</v>
       </c>
       <c r="B38" t="n">
         <v>74863</v>
@@ -4407,10 +4402,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>372261</v>
+        <v>372375</v>
       </c>
       <c r="R38" t="n">
-        <v>6934264</v>
+        <v>6934215</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,7 +4464,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122970155</v>
+        <v>122969637</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4509,10 +4504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>372059</v>
+        <v>372139</v>
       </c>
       <c r="R39" t="n">
-        <v>6934345</v>
+        <v>6934367</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,7 +4566,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122963972</v>
+        <v>122965361</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -4607,14 +4602,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>372274</v>
+        <v>372585</v>
       </c>
       <c r="R40" t="n">
-        <v>6934163</v>
+        <v>6934042</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,7 +4668,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122970659</v>
+        <v>122970500</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4713,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>372348</v>
+        <v>372318</v>
       </c>
       <c r="R41" t="n">
-        <v>6934275</v>
+        <v>6934300</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4775,10 +4770,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122965070</v>
+        <v>122970429</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4791,42 +4786,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>372491</v>
+        <v>372253</v>
       </c>
       <c r="R42" t="n">
-        <v>6934104</v>
+        <v>6934293</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4882,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122967925</v>
+        <v>122965070</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4898,37 +4888,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>372457</v>
+        <v>372491</v>
       </c>
       <c r="R43" t="n">
-        <v>6934206</v>
+        <v>6934104</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4984,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122969914</v>
+        <v>122970713</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5000,37 +4995,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>372129</v>
+        <v>372362</v>
       </c>
       <c r="R44" t="n">
-        <v>6934375</v>
+        <v>6934267</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122963595</v>
+        <v>122965141</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5122,14 +5122,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>372223</v>
+        <v>372528</v>
       </c>
       <c r="R45" t="n">
-        <v>6934198</v>
+        <v>6934080</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,10 +5188,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122968312</v>
+        <v>122960937</v>
       </c>
       <c r="B46" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5204,21 +5204,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>372375</v>
+        <v>372056</v>
       </c>
       <c r="R46" t="n">
-        <v>6934215</v>
+        <v>6934270</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122966267</v>
+        <v>122967646</v>
       </c>
       <c r="B47" t="n">
         <v>78766</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>372606</v>
+        <v>372519</v>
       </c>
       <c r="R47" t="n">
-        <v>6934099</v>
+        <v>6934145</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122969637</v>
+        <v>122965746</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5408,34 +5408,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>372139</v>
+        <v>372716</v>
       </c>
       <c r="R48" t="n">
-        <v>6934367</v>
+        <v>6934036</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,7 +5494,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122970143</v>
+        <v>122969914</v>
       </c>
       <c r="B49" t="n">
         <v>78766</v>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>372099</v>
+        <v>372129</v>
       </c>
       <c r="R49" t="n">
-        <v>6934362</v>
+        <v>6934375</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122960569</v>
+        <v>122970155</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -5636,10 +5636,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>372015</v>
+        <v>372059</v>
       </c>
       <c r="R50" t="n">
-        <v>6934298</v>
+        <v>6934345</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5698,10 +5698,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122965564</v>
+        <v>122962156</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5714,34 +5714,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>372662</v>
+        <v>372213</v>
       </c>
       <c r="R51" t="n">
-        <v>6934028</v>
+        <v>6934190</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5800,7 +5800,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122969456</v>
+        <v>122965816</v>
       </c>
       <c r="B52" t="n">
         <v>74863</v>
@@ -5836,14 +5836,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>372175</v>
+        <v>372684</v>
       </c>
       <c r="R52" t="n">
-        <v>6934323</v>
+        <v>6934056</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5902,7 +5902,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122968616</v>
+        <v>122967925</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>372302</v>
+        <v>372457</v>
       </c>
       <c r="R53" t="n">
-        <v>6934249</v>
+        <v>6934206</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122969444</v>
+        <v>122969275</v>
       </c>
       <c r="B54" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6020,34 +6020,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>372175</v>
+        <v>372204</v>
       </c>
       <c r="R54" t="n">
-        <v>6934323</v>
+        <v>6934300</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6106,10 +6106,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122967574</v>
+        <v>122968171</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6122,42 +6122,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>372536</v>
+        <v>372420</v>
       </c>
       <c r="R55" t="n">
-        <v>6934127</v>
+        <v>6934199</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6213,10 +6208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122970713</v>
+        <v>122965016</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6229,42 +6224,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>372362</v>
+        <v>372465</v>
       </c>
       <c r="R56" t="n">
-        <v>6934267</v>
+        <v>6934107</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6320,10 +6310,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122962287</v>
+        <v>122969955</v>
       </c>
       <c r="B57" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6332,20 +6322,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6354,19 +6344,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>372237</v>
+        <v>372131</v>
       </c>
       <c r="R57" t="n">
-        <v>6934196</v>
+        <v>6934388</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6422,10 +6417,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122961339</v>
+        <v>122961738</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6438,37 +6433,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>372139</v>
+        <v>372193</v>
       </c>
       <c r="R58" t="n">
-        <v>6934261</v>
+        <v>6934231</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122969270</v>
+        <v>122967699</v>
       </c>
       <c r="B59" t="n">
         <v>90970</v>
@@ -6560,14 +6560,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>372204</v>
+        <v>372504</v>
       </c>
       <c r="R59" t="n">
-        <v>6934300</v>
+        <v>6934172</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6626,10 +6626,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122965816</v>
+        <v>122968318</v>
       </c>
       <c r="B60" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6642,34 +6642,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>372684</v>
+        <v>372375</v>
       </c>
       <c r="R60" t="n">
-        <v>6934056</v>
+        <v>6934215</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6728,10 +6728,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122968318</v>
+        <v>122968972</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6744,21 +6744,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>372375</v>
+        <v>372261</v>
       </c>
       <c r="R61" t="n">
-        <v>6934215</v>
+        <v>6934264</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6830,10 +6830,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122969275</v>
+        <v>122968248</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>90948</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6846,34 +6846,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>372204</v>
+        <v>372404</v>
       </c>
       <c r="R62" t="n">
-        <v>6934300</v>
+        <v>6934224</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,7 +6932,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122970429</v>
+        <v>122964107</v>
       </c>
       <c r="B63" t="n">
         <v>78766</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>372253</v>
+        <v>372305</v>
       </c>
       <c r="R63" t="n">
-        <v>6934293</v>
+        <v>6934147</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,7 +7034,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122970500</v>
+        <v>122967390</v>
       </c>
       <c r="B64" t="n">
         <v>78766</v>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>372318</v>
+        <v>372563</v>
       </c>
       <c r="R64" t="n">
-        <v>6934300</v>
+        <v>6934123</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122963587</v>
+        <v>122968966</v>
       </c>
       <c r="B65" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>372223</v>
+        <v>372261</v>
       </c>
       <c r="R65" t="n">
-        <v>6934198</v>
+        <v>6934264</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122960937</v>
+        <v>122966267</v>
       </c>
       <c r="B66" t="n">
         <v>78766</v>
@@ -7274,14 +7274,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>372056</v>
+        <v>372606</v>
       </c>
       <c r="R66" t="n">
-        <v>6934270</v>
+        <v>6934099</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122962156</v>
+        <v>122968399</v>
       </c>
       <c r="B67" t="n">
-        <v>90970</v>
+        <v>79876</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7352,25 +7352,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>372213</v>
+        <v>372360</v>
       </c>
       <c r="R67" t="n">
-        <v>6934190</v>
+        <v>6934228</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122969101</v>
+        <v>122961215</v>
       </c>
       <c r="B68" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7458,21 +7458,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>372244</v>
+        <v>372104</v>
       </c>
       <c r="R68" t="n">
-        <v>6934274</v>
+        <v>6934254</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122961339</v>
+        <v>122961588</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372139</v>
+        <v>372194</v>
       </c>
       <c r="R11" t="n">
-        <v>6934261</v>
+        <v>6934243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122961461</v>
+        <v>122968306</v>
       </c>
       <c r="B12" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372167</v>
+        <v>372375</v>
       </c>
       <c r="R12" t="n">
-        <v>6934263</v>
+        <v>6934215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122969444</v>
+        <v>122961339</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372175</v>
+        <v>372139</v>
       </c>
       <c r="R13" t="n">
-        <v>6934323</v>
+        <v>6934261</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122961588</v>
+        <v>122961461</v>
       </c>
       <c r="B14" t="n">
-        <v>90952</v>
+        <v>74863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372194</v>
+        <v>372167</v>
       </c>
       <c r="R14" t="n">
-        <v>6934243</v>
+        <v>6934263</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122968306</v>
+        <v>122969444</v>
       </c>
       <c r="B15" t="n">
-        <v>82553</v>
+        <v>90970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372375</v>
+        <v>372175</v>
       </c>
       <c r="R15" t="n">
-        <v>6934215</v>
+        <v>6934323</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -4362,10 +4362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122968312</v>
+        <v>122965070</v>
       </c>
       <c r="B38" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4378,37 +4378,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>372375</v>
+        <v>372491</v>
       </c>
       <c r="R38" t="n">
-        <v>6934215</v>
+        <v>6934104</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4464,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122969637</v>
+        <v>122970713</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4480,37 +4485,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>372139</v>
+        <v>372362</v>
       </c>
       <c r="R39" t="n">
-        <v>6934367</v>
+        <v>6934267</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4566,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122965361</v>
+        <v>122968312</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4582,34 +4592,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>372585</v>
+        <v>372375</v>
       </c>
       <c r="R40" t="n">
-        <v>6934042</v>
+        <v>6934215</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4668,7 +4678,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122970500</v>
+        <v>122969637</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4704,14 +4714,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>372318</v>
+        <v>372139</v>
       </c>
       <c r="R41" t="n">
-        <v>6934300</v>
+        <v>6934367</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,7 +4780,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122970429</v>
+        <v>122965361</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4806,14 +4816,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>372253</v>
+        <v>372585</v>
       </c>
       <c r="R42" t="n">
-        <v>6934293</v>
+        <v>6934042</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4872,10 +4882,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122965070</v>
+        <v>122970500</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4888,42 +4898,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>372491</v>
+        <v>372318</v>
       </c>
       <c r="R43" t="n">
-        <v>6934104</v>
+        <v>6934300</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4979,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122970713</v>
+        <v>122970429</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,42 +5000,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>372362</v>
+        <v>372253</v>
       </c>
       <c r="R44" t="n">
-        <v>6934267</v>
+        <v>6934293</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122968966</v>
+        <v>122966267</v>
       </c>
       <c r="B65" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7152,34 +7152,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>372261</v>
+        <v>372606</v>
       </c>
       <c r="R65" t="n">
-        <v>6934264</v>
+        <v>6934099</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122966267</v>
+        <v>122968399</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7250,38 +7250,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>372606</v>
+        <v>372360</v>
       </c>
       <c r="R66" t="n">
-        <v>6934099</v>
+        <v>6934228</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122968399</v>
+        <v>122961215</v>
       </c>
       <c r="B67" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7352,25 +7352,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>372360</v>
+        <v>372104</v>
       </c>
       <c r="R67" t="n">
-        <v>6934228</v>
+        <v>6934254</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122961215</v>
+        <v>122968966</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7458,21 +7458,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>372104</v>
+        <v>372261</v>
       </c>
       <c r="R68" t="n">
-        <v>6934254</v>
+        <v>6934264</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122962287</v>
+        <v>122965564</v>
       </c>
       <c r="B7" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,41 +1197,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372237</v>
+        <v>372662</v>
       </c>
       <c r="R7" t="n">
-        <v>6934196</v>
+        <v>6934028</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122965564</v>
+        <v>122963587</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372662</v>
+        <v>372223</v>
       </c>
       <c r="R8" t="n">
-        <v>6934028</v>
+        <v>6934198</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122963587</v>
+        <v>122961601</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372223</v>
+        <v>372194</v>
       </c>
       <c r="R9" t="n">
-        <v>6934198</v>
+        <v>6934243</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122961601</v>
+        <v>122962287</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372194</v>
+        <v>372237</v>
       </c>
       <c r="R10" t="n">
-        <v>6934243</v>
+        <v>6934196</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122961588</v>
+        <v>122961339</v>
       </c>
       <c r="B11" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372194</v>
+        <v>372139</v>
       </c>
       <c r="R11" t="n">
-        <v>6934243</v>
+        <v>6934261</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122968306</v>
+        <v>122961461</v>
       </c>
       <c r="B12" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372375</v>
+        <v>372167</v>
       </c>
       <c r="R12" t="n">
-        <v>6934215</v>
+        <v>6934263</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122961339</v>
+        <v>122969444</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372139</v>
+        <v>372175</v>
       </c>
       <c r="R13" t="n">
-        <v>6934261</v>
+        <v>6934323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122961461</v>
+        <v>122961588</v>
       </c>
       <c r="B14" t="n">
-        <v>74863</v>
+        <v>90952</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372167</v>
+        <v>372194</v>
       </c>
       <c r="R14" t="n">
-        <v>6934263</v>
+        <v>6934243</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122969444</v>
+        <v>122968306</v>
       </c>
       <c r="B15" t="n">
-        <v>90970</v>
+        <v>82553</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372175</v>
+        <v>372375</v>
       </c>
       <c r="R15" t="n">
-        <v>6934323</v>
+        <v>6934215</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122965447</v>
+        <v>122969456</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,42 +3144,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>372613</v>
+        <v>372175</v>
       </c>
       <c r="R26" t="n">
-        <v>6934029</v>
+        <v>6934323</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3235,7 +3230,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122969456</v>
+        <v>122961144</v>
       </c>
       <c r="B27" t="n">
         <v>74863</v>
@@ -3275,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>372175</v>
+        <v>372056</v>
       </c>
       <c r="R27" t="n">
-        <v>6934323</v>
+        <v>6934270</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122961144</v>
+        <v>122965447</v>
       </c>
       <c r="B28" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,37 +3348,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>372056</v>
+        <v>372613</v>
       </c>
       <c r="R28" t="n">
-        <v>6934270</v>
+        <v>6934029</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122969270</v>
+        <v>122970239</v>
       </c>
       <c r="B36" t="n">
-        <v>90970</v>
+        <v>74863</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4174,34 +4174,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>372204</v>
+        <v>372139</v>
       </c>
       <c r="R36" t="n">
-        <v>6934300</v>
+        <v>6934344</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122970239</v>
+        <v>122969270</v>
       </c>
       <c r="B37" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4276,34 +4276,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>372139</v>
+        <v>372204</v>
       </c>
       <c r="R37" t="n">
-        <v>6934344</v>
+        <v>6934300</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4362,10 +4362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122965070</v>
+        <v>122968312</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4378,42 +4378,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>372491</v>
+        <v>372375</v>
       </c>
       <c r="R38" t="n">
-        <v>6934104</v>
+        <v>6934215</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4469,10 +4464,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122970713</v>
+        <v>122969637</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4485,42 +4480,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>372362</v>
+        <v>372139</v>
       </c>
       <c r="R39" t="n">
-        <v>6934267</v>
+        <v>6934367</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4576,10 +4566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122968312</v>
+        <v>122965361</v>
       </c>
       <c r="B40" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4592,34 +4582,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>372375</v>
+        <v>372585</v>
       </c>
       <c r="R40" t="n">
-        <v>6934215</v>
+        <v>6934042</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,7 +4668,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122969637</v>
+        <v>122970500</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4714,14 +4704,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>372139</v>
+        <v>372318</v>
       </c>
       <c r="R41" t="n">
-        <v>6934367</v>
+        <v>6934300</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,7 +4770,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122965361</v>
+        <v>122970429</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4816,14 +4806,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>372585</v>
+        <v>372253</v>
       </c>
       <c r="R42" t="n">
-        <v>6934042</v>
+        <v>6934293</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122970500</v>
+        <v>122965070</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4898,37 +4888,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>372318</v>
+        <v>372491</v>
       </c>
       <c r="R43" t="n">
-        <v>6934300</v>
+        <v>6934104</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4984,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122970429</v>
+        <v>122970713</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5000,37 +4995,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>372253</v>
+        <v>372362</v>
       </c>
       <c r="R44" t="n">
-        <v>6934293</v>
+        <v>6934267</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122966267</v>
+        <v>122968966</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7152,34 +7152,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>372606</v>
+        <v>372261</v>
       </c>
       <c r="R65" t="n">
-        <v>6934099</v>
+        <v>6934264</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122968399</v>
+        <v>122966267</v>
       </c>
       <c r="B66" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7250,38 +7250,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>372360</v>
+        <v>372606</v>
       </c>
       <c r="R66" t="n">
-        <v>6934228</v>
+        <v>6934099</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122961215</v>
+        <v>122968399</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7352,25 +7352,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>372104</v>
+        <v>372360</v>
       </c>
       <c r="R67" t="n">
-        <v>6934254</v>
+        <v>6934228</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122968966</v>
+        <v>122961215</v>
       </c>
       <c r="B68" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7458,21 +7458,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>372261</v>
+        <v>372104</v>
       </c>
       <c r="R68" t="n">
-        <v>6934264</v>
+        <v>6934254</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122963972</v>
+        <v>122969955</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372274</v>
+        <v>372131</v>
       </c>
       <c r="R2" t="n">
-        <v>6934163</v>
+        <v>6934388</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122965272</v>
+        <v>122963972</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372519</v>
+        <v>372274</v>
       </c>
       <c r="R3" t="n">
-        <v>6934058</v>
+        <v>6934163</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122968525</v>
+        <v>122970500</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -915,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372330</v>
+        <v>372318</v>
       </c>
       <c r="R4" t="n">
-        <v>6934242</v>
+        <v>6934300</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122964992</v>
+        <v>122969456</v>
       </c>
       <c r="B5" t="n">
         <v>74863</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372465</v>
+        <v>372175</v>
       </c>
       <c r="R5" t="n">
-        <v>6934107</v>
+        <v>6934323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122965907</v>
+        <v>122968616</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1119,14 +1124,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372645</v>
+        <v>372302</v>
       </c>
       <c r="R6" t="n">
-        <v>6934077</v>
+        <v>6934249</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122965564</v>
+        <v>122970496</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372662</v>
+        <v>372318</v>
       </c>
       <c r="R7" t="n">
-        <v>6934028</v>
+        <v>6934300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122963587</v>
+        <v>122965447</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1308,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372223</v>
+        <v>372613</v>
       </c>
       <c r="R8" t="n">
-        <v>6934198</v>
+        <v>6934029</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122961601</v>
+        <v>122961215</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372194</v>
+        <v>372104</v>
       </c>
       <c r="R9" t="n">
-        <v>6934243</v>
+        <v>6934254</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122962287</v>
+        <v>122965361</v>
       </c>
       <c r="B10" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,41 +1513,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372237</v>
+        <v>372585</v>
       </c>
       <c r="R10" t="n">
-        <v>6934196</v>
+        <v>6934042</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122961339</v>
+        <v>122968318</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1633,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372139</v>
+        <v>372375</v>
       </c>
       <c r="R11" t="n">
-        <v>6934261</v>
+        <v>6934215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122961461</v>
+        <v>122970429</v>
       </c>
       <c r="B12" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372167</v>
+        <v>372253</v>
       </c>
       <c r="R12" t="n">
-        <v>6934263</v>
+        <v>6934293</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122969444</v>
+        <v>122970155</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372175</v>
+        <v>372059</v>
       </c>
       <c r="R13" t="n">
-        <v>6934323</v>
+        <v>6934345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122961588</v>
+        <v>122961738</v>
       </c>
       <c r="B14" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,37 +1925,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372194</v>
+        <v>372193</v>
       </c>
       <c r="R14" t="n">
-        <v>6934243</v>
+        <v>6934231</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2001,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122968306</v>
+        <v>122970713</v>
       </c>
       <c r="B15" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,37 +2032,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372375</v>
+        <v>372362</v>
       </c>
       <c r="R15" t="n">
-        <v>6934215</v>
+        <v>6934267</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2103,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122968251</v>
+        <v>122962156</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372404</v>
+        <v>372213</v>
       </c>
       <c r="R16" t="n">
-        <v>6934224</v>
+        <v>6934190</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122970143</v>
+        <v>122965816</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,34 +2343,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>372099</v>
+        <v>372684</v>
       </c>
       <c r="R18" t="n">
-        <v>6934362</v>
+        <v>6934056</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122963945</v>
+        <v>122965746</v>
       </c>
       <c r="B19" t="n">
         <v>74863</v>
@@ -2445,14 +2465,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>372274</v>
+        <v>372716</v>
       </c>
       <c r="R19" t="n">
-        <v>6934163</v>
+        <v>6934036</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2531,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122970638</v>
+        <v>122967574</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2556,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>372342</v>
+        <v>372536</v>
       </c>
       <c r="R20" t="n">
-        <v>6934292</v>
+        <v>6934127</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2618,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122969120</v>
+        <v>122962287</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2650,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,13 +2678,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>372226</v>
+        <v>372237</v>
       </c>
       <c r="R21" t="n">
-        <v>6934263</v>
+        <v>6934196</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,7 +2740,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122970659</v>
+        <v>122965141</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2760,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>372348</v>
+        <v>372528</v>
       </c>
       <c r="R22" t="n">
-        <v>6934275</v>
+        <v>6934080</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122963595</v>
+        <v>122968306</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>372223</v>
+        <v>372375</v>
       </c>
       <c r="R23" t="n">
-        <v>6934198</v>
+        <v>6934215</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122970496</v>
+        <v>122968312</v>
       </c>
       <c r="B24" t="n">
-        <v>90970</v>
+        <v>74863</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,34 +2960,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>372318</v>
+        <v>372375</v>
       </c>
       <c r="R24" t="n">
-        <v>6934300</v>
+        <v>6934215</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122970193</v>
+        <v>122968251</v>
       </c>
       <c r="B25" t="n">
-        <v>90948</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3062,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>372119</v>
+        <v>372404</v>
       </c>
       <c r="R25" t="n">
-        <v>6934355</v>
+        <v>6934224</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122969456</v>
+        <v>122967390</v>
       </c>
       <c r="B26" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,34 +3164,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>372175</v>
+        <v>372563</v>
       </c>
       <c r="R26" t="n">
-        <v>6934323</v>
+        <v>6934123</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122961144</v>
+        <v>122964107</v>
       </c>
       <c r="B27" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,21 +3266,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>372056</v>
+        <v>372305</v>
       </c>
       <c r="R27" t="n">
-        <v>6934270</v>
+        <v>6934147</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122965447</v>
+        <v>122967646</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,42 +3368,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>372613</v>
+        <v>372519</v>
       </c>
       <c r="R28" t="n">
-        <v>6934029</v>
+        <v>6934145</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3439,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122969101</v>
+        <v>122967925</v>
       </c>
       <c r="B29" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3470,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>372244</v>
+        <v>372457</v>
       </c>
       <c r="R29" t="n">
-        <v>6934274</v>
+        <v>6934206</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122967374</v>
+        <v>122968248</v>
       </c>
       <c r="B30" t="n">
-        <v>74863</v>
+        <v>90948</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,34 +3572,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>372563</v>
+        <v>372404</v>
       </c>
       <c r="R30" t="n">
-        <v>6934123</v>
+        <v>6934224</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122968129</v>
+        <v>122966267</v>
       </c>
       <c r="B31" t="n">
-        <v>91640</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3655,38 +3670,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>372441</v>
+        <v>372606</v>
       </c>
       <c r="R31" t="n">
-        <v>6934188</v>
+        <v>6934099</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122968061</v>
+        <v>122961601</v>
       </c>
       <c r="B32" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3776,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>372448</v>
+        <v>372194</v>
       </c>
       <c r="R32" t="n">
-        <v>6934207</v>
+        <v>6934243</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122960569</v>
+        <v>122969101</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3878,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>372015</v>
+        <v>372244</v>
       </c>
       <c r="R33" t="n">
-        <v>6934298</v>
+        <v>6934274</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122968616</v>
+        <v>122967374</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3965,34 +3980,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>372302</v>
+        <v>372563</v>
       </c>
       <c r="R34" t="n">
-        <v>6934249</v>
+        <v>6934123</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122967574</v>
+        <v>122968129</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>91640</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4063,46 +4078,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>372536</v>
+        <v>372441</v>
       </c>
       <c r="R35" t="n">
-        <v>6934127</v>
+        <v>6934188</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4158,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122970239</v>
+        <v>122969120</v>
       </c>
       <c r="B36" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4174,21 +4184,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4198,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>372139</v>
+        <v>372226</v>
       </c>
       <c r="R36" t="n">
-        <v>6934344</v>
+        <v>6934263</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4260,10 +4270,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122969270</v>
+        <v>122960569</v>
       </c>
       <c r="B37" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4276,34 +4286,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>372204</v>
+        <v>372015</v>
       </c>
       <c r="R37" t="n">
-        <v>6934300</v>
+        <v>6934298</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4362,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122968312</v>
+        <v>122969270</v>
       </c>
       <c r="B38" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4378,34 +4388,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>372375</v>
+        <v>372204</v>
       </c>
       <c r="R38" t="n">
-        <v>6934215</v>
+        <v>6934300</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4464,7 +4474,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122969637</v>
+        <v>122963595</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4504,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>372139</v>
+        <v>372223</v>
       </c>
       <c r="R39" t="n">
-        <v>6934367</v>
+        <v>6934198</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122965361</v>
+        <v>122967699</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4582,34 +4592,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>372585</v>
+        <v>372504</v>
       </c>
       <c r="R40" t="n">
-        <v>6934042</v>
+        <v>6934172</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4668,7 +4678,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122970500</v>
+        <v>122965016</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4704,14 +4714,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>372318</v>
+        <v>372465</v>
       </c>
       <c r="R41" t="n">
-        <v>6934300</v>
+        <v>6934107</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122970429</v>
+        <v>122968171</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4786,21 +4796,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4810,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>372253</v>
+        <v>372420</v>
       </c>
       <c r="R42" t="n">
-        <v>6934293</v>
+        <v>6934199</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4872,10 +4882,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122965070</v>
+        <v>122960937</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4888,42 +4898,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>372491</v>
+        <v>372056</v>
       </c>
       <c r="R43" t="n">
-        <v>6934104</v>
+        <v>6934270</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4979,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122970713</v>
+        <v>122961339</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,42 +5000,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>372362</v>
+        <v>372139</v>
       </c>
       <c r="R44" t="n">
-        <v>6934267</v>
+        <v>6934261</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5086,10 +5086,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122965141</v>
+        <v>122970239</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5102,34 +5102,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>372528</v>
+        <v>372139</v>
       </c>
       <c r="R45" t="n">
-        <v>6934080</v>
+        <v>6934344</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,10 +5188,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122960937</v>
+        <v>122968972</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5204,21 +5204,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>372056</v>
+        <v>372261</v>
       </c>
       <c r="R46" t="n">
-        <v>6934270</v>
+        <v>6934264</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,10 +5290,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122967646</v>
+        <v>122961588</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5306,34 +5306,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>372519</v>
+        <v>372194</v>
       </c>
       <c r="R47" t="n">
-        <v>6934145</v>
+        <v>6934243</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122965746</v>
+        <v>122968525</v>
       </c>
       <c r="B48" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5408,34 +5408,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>372716</v>
+        <v>372330</v>
       </c>
       <c r="R48" t="n">
-        <v>6934036</v>
+        <v>6934242</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122969914</v>
+        <v>122961144</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5510,21 +5510,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>372129</v>
+        <v>372056</v>
       </c>
       <c r="R49" t="n">
-        <v>6934375</v>
+        <v>6934270</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122970155</v>
+        <v>122965070</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5612,37 +5612,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>372059</v>
+        <v>372491</v>
       </c>
       <c r="R50" t="n">
-        <v>6934345</v>
+        <v>6934104</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5698,10 +5703,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122962156</v>
+        <v>122965564</v>
       </c>
       <c r="B51" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5714,34 +5719,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>372213</v>
+        <v>372662</v>
       </c>
       <c r="R51" t="n">
-        <v>6934190</v>
+        <v>6934028</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5800,7 +5805,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122965816</v>
+        <v>122964992</v>
       </c>
       <c r="B52" t="n">
         <v>74863</v>
@@ -5836,14 +5841,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>372684</v>
+        <v>372465</v>
       </c>
       <c r="R52" t="n">
-        <v>6934056</v>
+        <v>6934107</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5902,7 +5907,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122967925</v>
+        <v>122965907</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -5938,14 +5943,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>372457</v>
+        <v>372645</v>
       </c>
       <c r="R53" t="n">
-        <v>6934206</v>
+        <v>6934077</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6004,10 +6009,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122969275</v>
+        <v>122968399</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6016,38 +6021,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>372204</v>
+        <v>372360</v>
       </c>
       <c r="R54" t="n">
-        <v>6934300</v>
+        <v>6934228</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6106,10 +6111,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122968171</v>
+        <v>122970193</v>
       </c>
       <c r="B55" t="n">
-        <v>74863</v>
+        <v>90948</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6122,21 +6127,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6146,10 +6151,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>372420</v>
+        <v>372119</v>
       </c>
       <c r="R55" t="n">
-        <v>6934199</v>
+        <v>6934355</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6208,10 +6213,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122965016</v>
+        <v>122970638</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6224,37 +6229,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>372465</v>
+        <v>372342</v>
       </c>
       <c r="R56" t="n">
-        <v>6934107</v>
+        <v>6934292</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6310,10 +6320,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122969955</v>
+        <v>122969637</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6326,42 +6336,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>372131</v>
+        <v>372139</v>
       </c>
       <c r="R57" t="n">
-        <v>6934388</v>
+        <v>6934367</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6417,10 +6422,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122961738</v>
+        <v>122969275</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6433,42 +6438,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>372193</v>
+        <v>372204</v>
       </c>
       <c r="R58" t="n">
-        <v>6934231</v>
+        <v>6934300</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122967699</v>
+        <v>122968966</v>
       </c>
       <c r="B59" t="n">
-        <v>90970</v>
+        <v>82553</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6540,21 +6540,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>372504</v>
+        <v>372261</v>
       </c>
       <c r="R59" t="n">
-        <v>6934172</v>
+        <v>6934264</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6626,7 +6626,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122968318</v>
+        <v>122970659</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -6662,14 +6662,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>372375</v>
+        <v>372348</v>
       </c>
       <c r="R60" t="n">
-        <v>6934215</v>
+        <v>6934275</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6728,10 +6728,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122968972</v>
+        <v>122969914</v>
       </c>
       <c r="B61" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6744,21 +6744,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>372261</v>
+        <v>372129</v>
       </c>
       <c r="R61" t="n">
-        <v>6934264</v>
+        <v>6934375</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6830,10 +6830,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122968248</v>
+        <v>122969444</v>
       </c>
       <c r="B62" t="n">
-        <v>90948</v>
+        <v>90970</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6846,21 +6846,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>372404</v>
+        <v>372175</v>
       </c>
       <c r="R62" t="n">
-        <v>6934224</v>
+        <v>6934323</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122964107</v>
+        <v>122968061</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6948,21 +6948,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>372305</v>
+        <v>372448</v>
       </c>
       <c r="R63" t="n">
-        <v>6934147</v>
+        <v>6934207</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,7 +7034,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122967390</v>
+        <v>122970143</v>
       </c>
       <c r="B64" t="n">
         <v>78766</v>
@@ -7070,14 +7070,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>372563</v>
+        <v>372099</v>
       </c>
       <c r="R64" t="n">
-        <v>6934123</v>
+        <v>6934362</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122968966</v>
+        <v>122965272</v>
       </c>
       <c r="B65" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7152,34 +7152,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>372261</v>
+        <v>372519</v>
       </c>
       <c r="R65" t="n">
-        <v>6934264</v>
+        <v>6934058</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122966267</v>
+        <v>122963587</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7254,34 +7254,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>372606</v>
+        <v>372223</v>
       </c>
       <c r="R66" t="n">
-        <v>6934099</v>
+        <v>6934198</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122968399</v>
+        <v>122961461</v>
       </c>
       <c r="B67" t="n">
-        <v>79876</v>
+        <v>74863</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7352,25 +7352,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>372360</v>
+        <v>372167</v>
       </c>
       <c r="R67" t="n">
-        <v>6934228</v>
+        <v>6934263</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122961215</v>
+        <v>122963945</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7458,21 +7458,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>372104</v>
+        <v>372274</v>
       </c>
       <c r="R68" t="n">
-        <v>6934254</v>
+        <v>6934163</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122969955</v>
+        <v>122968525</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372131</v>
+        <v>372330</v>
       </c>
       <c r="R2" t="n">
-        <v>6934388</v>
+        <v>6934242</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122963972</v>
+        <v>122964107</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372274</v>
+        <v>372305</v>
       </c>
       <c r="R3" t="n">
-        <v>6934163</v>
+        <v>6934147</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122970500</v>
+        <v>122965564</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372318</v>
+        <v>372662</v>
       </c>
       <c r="R4" t="n">
-        <v>6934300</v>
+        <v>6934028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122969456</v>
+        <v>122967374</v>
       </c>
       <c r="B5" t="n">
         <v>74863</v>
@@ -1022,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372175</v>
+        <v>372563</v>
       </c>
       <c r="R5" t="n">
-        <v>6934323</v>
+        <v>6934123</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122968616</v>
+        <v>122970659</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1124,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372302</v>
+        <v>372348</v>
       </c>
       <c r="R6" t="n">
-        <v>6934249</v>
+        <v>6934275</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122970496</v>
+        <v>122968616</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372318</v>
+        <v>372302</v>
       </c>
       <c r="R7" t="n">
-        <v>6934300</v>
+        <v>6934249</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122965447</v>
+        <v>122968972</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,42 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372613</v>
+        <v>372261</v>
       </c>
       <c r="R8" t="n">
-        <v>6934029</v>
+        <v>6934264</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122961215</v>
+        <v>122963945</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372104</v>
+        <v>372274</v>
       </c>
       <c r="R9" t="n">
-        <v>6934254</v>
+        <v>6934163</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122965361</v>
+        <v>122970500</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372585</v>
+        <v>372318</v>
       </c>
       <c r="R10" t="n">
-        <v>6934042</v>
+        <v>6934300</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122968318</v>
+        <v>122970429</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372375</v>
+        <v>372253</v>
       </c>
       <c r="R11" t="n">
-        <v>6934215</v>
+        <v>6934293</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122970429</v>
+        <v>122969637</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1745,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372253</v>
+        <v>372139</v>
       </c>
       <c r="R12" t="n">
-        <v>6934293</v>
+        <v>6934367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122970155</v>
+        <v>122968399</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372059</v>
+        <v>372360</v>
       </c>
       <c r="R13" t="n">
-        <v>6934345</v>
+        <v>6934228</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122961738</v>
+        <v>122967390</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,42 +1915,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372193</v>
+        <v>372563</v>
       </c>
       <c r="R14" t="n">
-        <v>6934231</v>
+        <v>6934123</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2016,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122970713</v>
+        <v>122962156</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,42 +2017,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372362</v>
+        <v>372213</v>
       </c>
       <c r="R15" t="n">
-        <v>6934267</v>
+        <v>6934190</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2123,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122962156</v>
+        <v>122965816</v>
       </c>
       <c r="B16" t="n">
-        <v>90970</v>
+        <v>74863</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,34 +2119,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372213</v>
+        <v>372684</v>
       </c>
       <c r="R16" t="n">
-        <v>6934190</v>
+        <v>6934056</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122965818</v>
+        <v>122968318</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2261,14 +2241,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>372684</v>
+        <v>372375</v>
       </c>
       <c r="R17" t="n">
-        <v>6934056</v>
+        <v>6934215</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122965816</v>
+        <v>122968171</v>
       </c>
       <c r="B18" t="n">
         <v>74863</v>
@@ -2363,14 +2343,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>372684</v>
+        <v>372420</v>
       </c>
       <c r="R18" t="n">
-        <v>6934056</v>
+        <v>6934199</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122965746</v>
+        <v>122970155</v>
       </c>
       <c r="B19" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,34 +2425,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>372716</v>
+        <v>372059</v>
       </c>
       <c r="R19" t="n">
-        <v>6934036</v>
+        <v>6934345</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122967574</v>
+        <v>122961144</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,42 +2527,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>372536</v>
+        <v>372056</v>
       </c>
       <c r="R20" t="n">
-        <v>6934127</v>
+        <v>6934270</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2638,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122962287</v>
+        <v>122965746</v>
       </c>
       <c r="B21" t="n">
-        <v>57589</v>
+        <v>74863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,41 +2625,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>372237</v>
+        <v>372716</v>
       </c>
       <c r="R21" t="n">
-        <v>6934196</v>
+        <v>6934036</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2740,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122965141</v>
+        <v>122962287</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2752,41 +2727,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>372528</v>
+        <v>372237</v>
       </c>
       <c r="R22" t="n">
-        <v>6934080</v>
+        <v>6934196</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2842,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122968306</v>
+        <v>122968966</v>
       </c>
       <c r="B23" t="n">
         <v>82553</v>
@@ -2882,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>372375</v>
+        <v>372261</v>
       </c>
       <c r="R23" t="n">
-        <v>6934215</v>
+        <v>6934264</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122968312</v>
+        <v>122967699</v>
       </c>
       <c r="B24" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>372375</v>
+        <v>372504</v>
       </c>
       <c r="R24" t="n">
-        <v>6934215</v>
+        <v>6934172</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122968251</v>
+        <v>122968061</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>372404</v>
+        <v>372448</v>
       </c>
       <c r="R25" t="n">
-        <v>6934224</v>
+        <v>6934207</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122967390</v>
+        <v>122968251</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3184,14 +3159,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>372563</v>
+        <v>372404</v>
       </c>
       <c r="R26" t="n">
-        <v>6934123</v>
+        <v>6934224</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122964107</v>
+        <v>122965361</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3286,14 +3261,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>372305</v>
+        <v>372585</v>
       </c>
       <c r="R27" t="n">
-        <v>6934147</v>
+        <v>6934042</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122967646</v>
+        <v>122969955</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,37 +3343,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>372519</v>
+        <v>372131</v>
       </c>
       <c r="R28" t="n">
-        <v>6934145</v>
+        <v>6934388</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3454,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122967925</v>
+        <v>122961588</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,21 +3450,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>372457</v>
+        <v>372194</v>
       </c>
       <c r="R29" t="n">
-        <v>6934206</v>
+        <v>6934243</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122968248</v>
+        <v>122961339</v>
       </c>
       <c r="B30" t="n">
-        <v>90948</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3572,21 +3552,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>372404</v>
+        <v>372139</v>
       </c>
       <c r="R30" t="n">
-        <v>6934224</v>
+        <v>6934261</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,7 +3638,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122966267</v>
+        <v>122970143</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3694,14 +3674,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>372606</v>
+        <v>372099</v>
       </c>
       <c r="R31" t="n">
-        <v>6934099</v>
+        <v>6934362</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,10 +3740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122961601</v>
+        <v>122965447</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3776,37 +3756,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>372194</v>
+        <v>372613</v>
       </c>
       <c r="R32" t="n">
-        <v>6934243</v>
+        <v>6934029</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3862,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122969101</v>
+        <v>122969270</v>
       </c>
       <c r="B33" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3878,34 +3863,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>372244</v>
+        <v>372204</v>
       </c>
       <c r="R33" t="n">
-        <v>6934274</v>
+        <v>6934300</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122967374</v>
+        <v>122965141</v>
       </c>
       <c r="B34" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3980,21 +3965,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>372563</v>
+        <v>372528</v>
       </c>
       <c r="R34" t="n">
-        <v>6934123</v>
+        <v>6934080</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122968129</v>
+        <v>122969275</v>
       </c>
       <c r="B35" t="n">
-        <v>91640</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4078,38 +4063,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>372441</v>
+        <v>372204</v>
       </c>
       <c r="R35" t="n">
-        <v>6934188</v>
+        <v>6934300</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,10 +4153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122969120</v>
+        <v>122970638</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4184,37 +4169,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>372226</v>
+        <v>372342</v>
       </c>
       <c r="R36" t="n">
-        <v>6934263</v>
+        <v>6934292</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4270,7 +4260,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122960569</v>
+        <v>122965016</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4310,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>372015</v>
+        <v>372465</v>
       </c>
       <c r="R37" t="n">
-        <v>6934298</v>
+        <v>6934107</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122969270</v>
+        <v>122960937</v>
       </c>
       <c r="B38" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4388,34 +4378,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>372204</v>
+        <v>372056</v>
       </c>
       <c r="R38" t="n">
-        <v>6934300</v>
+        <v>6934270</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,7 +4464,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122963595</v>
+        <v>122961215</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4514,10 +4504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>372223</v>
+        <v>372104</v>
       </c>
       <c r="R39" t="n">
-        <v>6934198</v>
+        <v>6934254</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,10 +4566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122967699</v>
+        <v>122963587</v>
       </c>
       <c r="B40" t="n">
-        <v>90970</v>
+        <v>74863</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4592,21 +4582,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>372504</v>
+        <v>372223</v>
       </c>
       <c r="R40" t="n">
-        <v>6934172</v>
+        <v>6934198</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,7 +4668,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122965016</v>
+        <v>122961601</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4718,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>372465</v>
+        <v>372194</v>
       </c>
       <c r="R41" t="n">
-        <v>6934107</v>
+        <v>6934243</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,7 +4770,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122968171</v>
+        <v>122970239</v>
       </c>
       <c r="B42" t="n">
         <v>74863</v>
@@ -4820,10 +4810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>372420</v>
+        <v>372139</v>
       </c>
       <c r="R42" t="n">
-        <v>6934199</v>
+        <v>6934344</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122960937</v>
+        <v>122967574</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4898,37 +4888,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>372056</v>
+        <v>372536</v>
       </c>
       <c r="R43" t="n">
-        <v>6934270</v>
+        <v>6934127</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4984,7 +4979,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122961339</v>
+        <v>122965818</v>
       </c>
       <c r="B44" t="n">
         <v>78766</v>
@@ -5020,14 +5015,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>372139</v>
+        <v>372684</v>
       </c>
       <c r="R44" t="n">
-        <v>6934261</v>
+        <v>6934056</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,10 +5081,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122970239</v>
+        <v>122965907</v>
       </c>
       <c r="B45" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5102,34 +5097,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>372139</v>
+        <v>372645</v>
       </c>
       <c r="R45" t="n">
-        <v>6934344</v>
+        <v>6934077</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,10 +5183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122968972</v>
+        <v>122970496</v>
       </c>
       <c r="B46" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5204,34 +5199,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>372261</v>
+        <v>372318</v>
       </c>
       <c r="R46" t="n">
-        <v>6934264</v>
+        <v>6934300</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,10 +5285,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122961588</v>
+        <v>122963972</v>
       </c>
       <c r="B47" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5306,21 +5301,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5330,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>372194</v>
+        <v>372274</v>
       </c>
       <c r="R47" t="n">
-        <v>6934243</v>
+        <v>6934163</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,7 +5387,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122968525</v>
+        <v>122963595</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5432,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>372330</v>
+        <v>372223</v>
       </c>
       <c r="R48" t="n">
-        <v>6934242</v>
+        <v>6934198</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,7 +5489,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122961144</v>
+        <v>122961461</v>
       </c>
       <c r="B49" t="n">
         <v>74863</v>
@@ -5534,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>372056</v>
+        <v>372167</v>
       </c>
       <c r="R49" t="n">
-        <v>6934270</v>
+        <v>6934263</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5596,7 +5591,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122965070</v>
+        <v>122970713</v>
       </c>
       <c r="B50" t="n">
         <v>57478</v>
@@ -5637,14 +5632,14 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>372491</v>
+        <v>372362</v>
       </c>
       <c r="R50" t="n">
-        <v>6934104</v>
+        <v>6934267</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5703,7 +5698,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122965564</v>
+        <v>122967646</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -5743,10 +5738,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>372662</v>
+        <v>372519</v>
       </c>
       <c r="R51" t="n">
-        <v>6934028</v>
+        <v>6934145</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5805,10 +5800,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122964992</v>
+        <v>122967925</v>
       </c>
       <c r="B52" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5821,21 +5816,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5845,10 +5840,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>372465</v>
+        <v>372457</v>
       </c>
       <c r="R52" t="n">
-        <v>6934107</v>
+        <v>6934206</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5907,10 +5902,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122965907</v>
+        <v>122969101</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5923,34 +5918,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>372645</v>
+        <v>372244</v>
       </c>
       <c r="R53" t="n">
-        <v>6934077</v>
+        <v>6934274</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6009,10 +6004,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122968399</v>
+        <v>122961738</v>
       </c>
       <c r="B54" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6021,41 +6016,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>372360</v>
+        <v>372193</v>
       </c>
       <c r="R54" t="n">
-        <v>6934228</v>
+        <v>6934231</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6213,10 +6213,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122970638</v>
+        <v>122968248</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>90948</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6229,42 +6229,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>372342</v>
+        <v>372404</v>
       </c>
       <c r="R56" t="n">
-        <v>6934292</v>
+        <v>6934224</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6320,10 +6315,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122969637</v>
+        <v>122965070</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6336,37 +6331,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>372139</v>
+        <v>372491</v>
       </c>
       <c r="R57" t="n">
-        <v>6934367</v>
+        <v>6934104</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6422,10 +6422,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122969275</v>
+        <v>122968129</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>91640</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6434,38 +6434,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>372204</v>
+        <v>372441</v>
       </c>
       <c r="R58" t="n">
-        <v>6934300</v>
+        <v>6934188</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122968966</v>
+        <v>122969444</v>
       </c>
       <c r="B59" t="n">
-        <v>82553</v>
+        <v>90970</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6540,21 +6540,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>372261</v>
+        <v>372175</v>
       </c>
       <c r="R59" t="n">
-        <v>6934264</v>
+        <v>6934323</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6626,10 +6626,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122970659</v>
+        <v>122965272</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6642,21 +6642,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>372348</v>
+        <v>372519</v>
       </c>
       <c r="R60" t="n">
-        <v>6934275</v>
+        <v>6934058</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6728,10 +6728,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122969914</v>
+        <v>122968312</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6744,21 +6744,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>372129</v>
+        <v>372375</v>
       </c>
       <c r="R61" t="n">
-        <v>6934375</v>
+        <v>6934215</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6830,10 +6830,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122969444</v>
+        <v>122969120</v>
       </c>
       <c r="B62" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6846,21 +6846,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>372175</v>
+        <v>372226</v>
       </c>
       <c r="R62" t="n">
-        <v>6934323</v>
+        <v>6934263</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122968061</v>
+        <v>122969456</v>
       </c>
       <c r="B63" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6948,21 +6948,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>372448</v>
+        <v>372175</v>
       </c>
       <c r="R63" t="n">
-        <v>6934207</v>
+        <v>6934323</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,7 +7034,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122970143</v>
+        <v>122960569</v>
       </c>
       <c r="B64" t="n">
         <v>78766</v>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>372099</v>
+        <v>372015</v>
       </c>
       <c r="R64" t="n">
-        <v>6934362</v>
+        <v>6934298</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,7 +7136,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122965272</v>
+        <v>122964992</v>
       </c>
       <c r="B65" t="n">
         <v>74863</v>
@@ -7172,14 +7172,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>372519</v>
+        <v>372465</v>
       </c>
       <c r="R65" t="n">
-        <v>6934058</v>
+        <v>6934107</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122963587</v>
+        <v>122966267</v>
       </c>
       <c r="B66" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7254,34 +7254,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>372223</v>
+        <v>372606</v>
       </c>
       <c r="R66" t="n">
-        <v>6934198</v>
+        <v>6934099</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122961461</v>
+        <v>122969914</v>
       </c>
       <c r="B67" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7356,21 +7356,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>372167</v>
+        <v>372129</v>
       </c>
       <c r="R67" t="n">
-        <v>6934263</v>
+        <v>6934375</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122963945</v>
+        <v>122968306</v>
       </c>
       <c r="B68" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7458,21 +7458,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>372274</v>
+        <v>372375</v>
       </c>
       <c r="R68" t="n">
-        <v>6934163</v>
+        <v>6934215</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122969270</v>
+        <v>122970638</v>
       </c>
       <c r="B33" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,37 +3863,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>372204</v>
+        <v>372342</v>
       </c>
       <c r="R33" t="n">
-        <v>6934300</v>
+        <v>6934292</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3949,10 +3954,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122965141</v>
+        <v>122969270</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3965,21 +3970,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,10 +3994,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>372528</v>
+        <v>372204</v>
       </c>
       <c r="R34" t="n">
-        <v>6934080</v>
+        <v>6934300</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,7 +4056,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122969275</v>
+        <v>122965141</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4091,10 +4096,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>372204</v>
+        <v>372528</v>
       </c>
       <c r="R35" t="n">
-        <v>6934300</v>
+        <v>6934080</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,10 +4158,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122970638</v>
+        <v>122969275</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4169,42 +4174,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>372342</v>
+        <v>372204</v>
       </c>
       <c r="R36" t="n">
-        <v>6934292</v>
+        <v>6934300</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4872,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122967574</v>
+        <v>122970496</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4888,42 +4888,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>372536</v>
+        <v>372318</v>
       </c>
       <c r="R43" t="n">
-        <v>6934127</v>
+        <v>6934300</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5183,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122970496</v>
+        <v>122967574</v>
       </c>
       <c r="B46" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,37 +5194,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>372318</v>
+        <v>372536</v>
       </c>
       <c r="R46" t="n">
-        <v>6934300</v>
+        <v>6934127</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6422,10 +6422,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122968129</v>
+        <v>122965272</v>
       </c>
       <c r="B58" t="n">
-        <v>91640</v>
+        <v>74863</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6434,38 +6434,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>372441</v>
+        <v>372519</v>
       </c>
       <c r="R58" t="n">
-        <v>6934188</v>
+        <v>6934058</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122969444</v>
+        <v>122968129</v>
       </c>
       <c r="B59" t="n">
-        <v>90970</v>
+        <v>91640</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6536,25 +6536,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>372175</v>
+        <v>372441</v>
       </c>
       <c r="R59" t="n">
-        <v>6934323</v>
+        <v>6934188</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6626,10 +6626,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122965272</v>
+        <v>122969444</v>
       </c>
       <c r="B60" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6642,34 +6642,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>372519</v>
+        <v>372175</v>
       </c>
       <c r="R60" t="n">
-        <v>6934058</v>
+        <v>6934323</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -5698,10 +5698,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122967646</v>
+        <v>122970193</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>90948</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5714,34 +5714,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>372519</v>
+        <v>372119</v>
       </c>
       <c r="R51" t="n">
-        <v>6934145</v>
+        <v>6934355</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5800,7 +5800,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122967925</v>
+        <v>122967646</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -5836,14 +5836,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>372457</v>
+        <v>372519</v>
       </c>
       <c r="R52" t="n">
-        <v>6934206</v>
+        <v>6934145</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5902,10 +5902,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122969101</v>
+        <v>122967925</v>
       </c>
       <c r="B53" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5918,21 +5918,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>372244</v>
+        <v>372457</v>
       </c>
       <c r="R53" t="n">
-        <v>6934274</v>
+        <v>6934206</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122961738</v>
+        <v>122969101</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6020,42 +6020,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>372193</v>
+        <v>372244</v>
       </c>
       <c r="R54" t="n">
-        <v>6934231</v>
+        <v>6934274</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6111,10 +6106,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122970193</v>
+        <v>122961738</v>
       </c>
       <c r="B55" t="n">
-        <v>90948</v>
+        <v>57478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6127,37 +6122,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>372119</v>
+        <v>372193</v>
       </c>
       <c r="R55" t="n">
-        <v>6934355</v>
+        <v>6934231</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122968525</v>
+        <v>122961461</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>74866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372330</v>
+        <v>372167</v>
       </c>
       <c r="R2" t="n">
-        <v>6934242</v>
+        <v>6934263</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122964107</v>
+        <v>122961144</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>74866</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372305</v>
+        <v>372056</v>
       </c>
       <c r="R3" t="n">
-        <v>6934147</v>
+        <v>6934270</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122965564</v>
+        <v>122970143</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372662</v>
+        <v>372099</v>
       </c>
       <c r="R4" t="n">
-        <v>6934028</v>
+        <v>6934362</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122967374</v>
+        <v>122969444</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
+        <v>90973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372563</v>
+        <v>372175</v>
       </c>
       <c r="R5" t="n">
-        <v>6934123</v>
+        <v>6934323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122970659</v>
+        <v>122965016</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372348</v>
+        <v>372465</v>
       </c>
       <c r="R6" t="n">
-        <v>6934275</v>
+        <v>6934107</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122968616</v>
+        <v>122968306</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>82556</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372302</v>
+        <v>372375</v>
       </c>
       <c r="R7" t="n">
-        <v>6934249</v>
+        <v>6934215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122968972</v>
+        <v>122969101</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>74866</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372261</v>
+        <v>372244</v>
       </c>
       <c r="R8" t="n">
-        <v>6934264</v>
+        <v>6934274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122963945</v>
+        <v>122968248</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>90951</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372274</v>
+        <v>372404</v>
       </c>
       <c r="R9" t="n">
-        <v>6934163</v>
+        <v>6934224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122970500</v>
+        <v>122970155</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,14 +1527,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372318</v>
+        <v>372059</v>
       </c>
       <c r="R10" t="n">
-        <v>6934300</v>
+        <v>6934345</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122970429</v>
+        <v>122967646</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,14 +1629,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372253</v>
+        <v>372519</v>
       </c>
       <c r="R11" t="n">
-        <v>6934293</v>
+        <v>6934145</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122969637</v>
+        <v>122969275</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,14 +1731,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372139</v>
+        <v>372204</v>
       </c>
       <c r="R12" t="n">
-        <v>6934367</v>
+        <v>6934300</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122968399</v>
+        <v>122970193</v>
       </c>
       <c r="B13" t="n">
-        <v>79876</v>
+        <v>90951</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372360</v>
+        <v>372119</v>
       </c>
       <c r="R13" t="n">
-        <v>6934228</v>
+        <v>6934355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122967390</v>
+        <v>122965746</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>74866</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372563</v>
+        <v>372716</v>
       </c>
       <c r="R14" t="n">
-        <v>6934123</v>
+        <v>6934036</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122962156</v>
+        <v>122968171</v>
       </c>
       <c r="B15" t="n">
-        <v>90970</v>
+        <v>74866</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372213</v>
+        <v>372420</v>
       </c>
       <c r="R15" t="n">
-        <v>6934190</v>
+        <v>6934199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122965816</v>
+        <v>122970500</v>
       </c>
       <c r="B16" t="n">
-        <v>74863</v>
+        <v>78769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372684</v>
+        <v>372318</v>
       </c>
       <c r="R16" t="n">
-        <v>6934056</v>
+        <v>6934300</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122968318</v>
+        <v>122963972</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>372375</v>
+        <v>372274</v>
       </c>
       <c r="R17" t="n">
-        <v>6934215</v>
+        <v>6934163</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122968171</v>
+        <v>122960937</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>78769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>372420</v>
+        <v>372056</v>
       </c>
       <c r="R18" t="n">
-        <v>6934199</v>
+        <v>6934270</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122970155</v>
+        <v>122968312</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>74866</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>372059</v>
+        <v>372375</v>
       </c>
       <c r="R19" t="n">
-        <v>6934345</v>
+        <v>6934215</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122961144</v>
+        <v>122967925</v>
       </c>
       <c r="B20" t="n">
-        <v>74863</v>
+        <v>78769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>372056</v>
+        <v>372457</v>
       </c>
       <c r="R20" t="n">
-        <v>6934270</v>
+        <v>6934206</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122965746</v>
+        <v>122966267</v>
       </c>
       <c r="B21" t="n">
-        <v>74863</v>
+        <v>78769</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>372716</v>
+        <v>372606</v>
       </c>
       <c r="R21" t="n">
-        <v>6934036</v>
+        <v>6934099</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122962287</v>
+        <v>122965816</v>
       </c>
       <c r="B22" t="n">
-        <v>57589</v>
+        <v>74866</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,41 +2727,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>372237</v>
+        <v>372684</v>
       </c>
       <c r="R22" t="n">
-        <v>6934196</v>
+        <v>6934056</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122968966</v>
+        <v>122965070</v>
       </c>
       <c r="B23" t="n">
-        <v>82553</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,37 +2833,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>372261</v>
+        <v>372491</v>
       </c>
       <c r="R23" t="n">
-        <v>6934264</v>
+        <v>6934104</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2919,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122967699</v>
+        <v>122969456</v>
       </c>
       <c r="B24" t="n">
-        <v>90970</v>
+        <v>74866</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>372504</v>
+        <v>372175</v>
       </c>
       <c r="R24" t="n">
-        <v>6934172</v>
+        <v>6934323</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122968061</v>
+        <v>122967699</v>
       </c>
       <c r="B25" t="n">
-        <v>82553</v>
+        <v>90973</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>372448</v>
+        <v>372504</v>
       </c>
       <c r="R25" t="n">
-        <v>6934207</v>
+        <v>6934172</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122968251</v>
+        <v>122961339</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3163,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>372404</v>
+        <v>372139</v>
       </c>
       <c r="R26" t="n">
-        <v>6934224</v>
+        <v>6934261</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122965361</v>
+        <v>122965907</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>372585</v>
+        <v>372645</v>
       </c>
       <c r="R27" t="n">
-        <v>6934042</v>
+        <v>6934077</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122969955</v>
+        <v>122962287</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57592</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3339,20 +3344,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3361,24 +3366,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>372131</v>
+        <v>372237</v>
       </c>
       <c r="R28" t="n">
-        <v>6934388</v>
+        <v>6934196</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122961588</v>
+        <v>122968061</v>
       </c>
       <c r="B29" t="n">
-        <v>90952</v>
+        <v>82556</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>372194</v>
+        <v>372448</v>
       </c>
       <c r="R29" t="n">
-        <v>6934243</v>
+        <v>6934207</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122961339</v>
+        <v>122967390</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3572,14 +3572,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>372139</v>
+        <v>372563</v>
       </c>
       <c r="R30" t="n">
-        <v>6934261</v>
+        <v>6934123</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122970143</v>
+        <v>122967374</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>74866</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3654,34 +3654,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>372099</v>
+        <v>372563</v>
       </c>
       <c r="R31" t="n">
-        <v>6934362</v>
+        <v>6934123</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122965447</v>
+        <v>122963945</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>74866</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3756,42 +3756,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>372613</v>
+        <v>372274</v>
       </c>
       <c r="R32" t="n">
-        <v>6934029</v>
+        <v>6934163</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3847,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122970638</v>
+        <v>122964992</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>74866</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,42 +3858,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>372342</v>
+        <v>372465</v>
       </c>
       <c r="R33" t="n">
-        <v>6934292</v>
+        <v>6934107</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3954,10 +3944,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122969270</v>
+        <v>122968251</v>
       </c>
       <c r="B34" t="n">
-        <v>90970</v>
+        <v>78769</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3970,34 +3960,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>372204</v>
+        <v>372404</v>
       </c>
       <c r="R34" t="n">
-        <v>6934300</v>
+        <v>6934224</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,10 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122965141</v>
+        <v>122965361</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4096,10 +4086,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>372528</v>
+        <v>372585</v>
       </c>
       <c r="R35" t="n">
-        <v>6934080</v>
+        <v>6934042</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4158,10 +4148,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122969275</v>
+        <v>122968966</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>82556</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4174,34 +4164,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>372204</v>
+        <v>372261</v>
       </c>
       <c r="R36" t="n">
-        <v>6934300</v>
+        <v>6934264</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4260,10 +4250,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122965016</v>
+        <v>122969914</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4300,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>372465</v>
+        <v>372129</v>
       </c>
       <c r="R37" t="n">
-        <v>6934107</v>
+        <v>6934375</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4362,10 +4352,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122960937</v>
+        <v>122968399</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>79879</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4374,25 +4364,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4402,10 +4392,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>372056</v>
+        <v>372360</v>
       </c>
       <c r="R38" t="n">
-        <v>6934270</v>
+        <v>6934228</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4464,10 +4454,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122961215</v>
+        <v>122970239</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>74866</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4480,21 +4470,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4504,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>372104</v>
+        <v>372139</v>
       </c>
       <c r="R39" t="n">
-        <v>6934254</v>
+        <v>6934344</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,10 +4556,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122963587</v>
+        <v>122970659</v>
       </c>
       <c r="B40" t="n">
-        <v>74863</v>
+        <v>78769</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4582,34 +4572,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>372223</v>
+        <v>372348</v>
       </c>
       <c r="R40" t="n">
-        <v>6934198</v>
+        <v>6934275</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4668,10 +4658,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122961601</v>
+        <v>122965141</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4704,14 +4694,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>372194</v>
+        <v>372528</v>
       </c>
       <c r="R41" t="n">
-        <v>6934243</v>
+        <v>6934080</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,10 +4760,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122970239</v>
+        <v>122970496</v>
       </c>
       <c r="B42" t="n">
-        <v>74863</v>
+        <v>90973</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4786,34 +4776,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>372139</v>
+        <v>372318</v>
       </c>
       <c r="R42" t="n">
-        <v>6934344</v>
+        <v>6934300</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4872,10 +4862,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122970496</v>
+        <v>122963587</v>
       </c>
       <c r="B43" t="n">
-        <v>90970</v>
+        <v>74866</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4888,34 +4878,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>372318</v>
+        <v>372223</v>
       </c>
       <c r="R43" t="n">
-        <v>6934300</v>
+        <v>6934198</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,10 +4964,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122965818</v>
+        <v>122968129</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>91643</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4986,38 +4976,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>372684</v>
+        <v>372441</v>
       </c>
       <c r="R44" t="n">
-        <v>6934056</v>
+        <v>6934188</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5076,10 +5066,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122965907</v>
+        <v>122968525</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5112,14 +5102,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>372645</v>
+        <v>372330</v>
       </c>
       <c r="R45" t="n">
-        <v>6934077</v>
+        <v>6934242</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5178,10 +5168,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122967574</v>
+        <v>122961601</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5194,42 +5184,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>372536</v>
+        <v>372194</v>
       </c>
       <c r="R46" t="n">
-        <v>6934127</v>
+        <v>6934243</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5285,10 +5270,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122963972</v>
+        <v>122969120</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5325,10 +5310,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>372274</v>
+        <v>372226</v>
       </c>
       <c r="R47" t="n">
-        <v>6934163</v>
+        <v>6934263</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5387,10 +5372,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122963595</v>
+        <v>122961215</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5427,10 +5412,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>372223</v>
+        <v>372104</v>
       </c>
       <c r="R48" t="n">
-        <v>6934198</v>
+        <v>6934254</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,10 +5474,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122961461</v>
+        <v>122965818</v>
       </c>
       <c r="B49" t="n">
-        <v>74863</v>
+        <v>78769</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,34 +5490,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>372167</v>
+        <v>372684</v>
       </c>
       <c r="R49" t="n">
-        <v>6934263</v>
+        <v>6934056</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5576,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122970713</v>
+        <v>122968318</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,42 +5592,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>372362</v>
+        <v>372375</v>
       </c>
       <c r="R50" t="n">
-        <v>6934267</v>
+        <v>6934215</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5698,10 +5678,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122970193</v>
+        <v>122970713</v>
       </c>
       <c r="B51" t="n">
-        <v>90948</v>
+        <v>57481</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5714,37 +5694,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>372119</v>
+        <v>372362</v>
       </c>
       <c r="R51" t="n">
-        <v>6934355</v>
+        <v>6934267</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5800,10 +5785,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122967646</v>
+        <v>122968616</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5836,14 +5821,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>372519</v>
+        <v>372302</v>
       </c>
       <c r="R52" t="n">
-        <v>6934145</v>
+        <v>6934249</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5902,10 +5887,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122967925</v>
+        <v>122963595</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5942,10 +5927,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>372457</v>
+        <v>372223</v>
       </c>
       <c r="R53" t="n">
-        <v>6934206</v>
+        <v>6934198</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6004,10 +5989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122969101</v>
+        <v>122965272</v>
       </c>
       <c r="B54" t="n">
-        <v>74863</v>
+        <v>74866</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6040,14 +6025,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>372244</v>
+        <v>372519</v>
       </c>
       <c r="R54" t="n">
-        <v>6934274</v>
+        <v>6934058</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6106,10 +6091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122961738</v>
+        <v>122969955</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6151,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>372193</v>
+        <v>372131</v>
       </c>
       <c r="R55" t="n">
-        <v>6934231</v>
+        <v>6934388</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6213,10 +6198,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122968248</v>
+        <v>122965447</v>
       </c>
       <c r="B56" t="n">
-        <v>90948</v>
+        <v>57481</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6229,37 +6214,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>372404</v>
+        <v>372613</v>
       </c>
       <c r="R56" t="n">
-        <v>6934224</v>
+        <v>6934029</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6315,10 +6305,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122965070</v>
+        <v>122965564</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6331,42 +6321,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>372491</v>
+        <v>372662</v>
       </c>
       <c r="R57" t="n">
-        <v>6934104</v>
+        <v>6934028</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6422,10 +6407,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122965272</v>
+        <v>122961588</v>
       </c>
       <c r="B58" t="n">
-        <v>74863</v>
+        <v>90955</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6438,34 +6423,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>372519</v>
+        <v>372194</v>
       </c>
       <c r="R58" t="n">
-        <v>6934058</v>
+        <v>6934243</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6524,10 +6509,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122968129</v>
+        <v>122969270</v>
       </c>
       <c r="B59" t="n">
-        <v>91640</v>
+        <v>90973</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6536,38 +6521,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>372441</v>
+        <v>372204</v>
       </c>
       <c r="R59" t="n">
-        <v>6934188</v>
+        <v>6934300</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6626,10 +6611,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122969444</v>
+        <v>122961738</v>
       </c>
       <c r="B60" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6642,37 +6627,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>372175</v>
+        <v>372193</v>
       </c>
       <c r="R60" t="n">
-        <v>6934323</v>
+        <v>6934231</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6728,10 +6718,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122968312</v>
+        <v>122968972</v>
       </c>
       <c r="B61" t="n">
-        <v>74863</v>
+        <v>74866</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6768,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>372375</v>
+        <v>372261</v>
       </c>
       <c r="R61" t="n">
-        <v>6934215</v>
+        <v>6934264</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6830,10 +6820,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122969120</v>
+        <v>122969637</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6870,10 +6860,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>372226</v>
+        <v>372139</v>
       </c>
       <c r="R62" t="n">
-        <v>6934263</v>
+        <v>6934367</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,10 +6922,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122969456</v>
+        <v>122960569</v>
       </c>
       <c r="B63" t="n">
-        <v>74863</v>
+        <v>78769</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6948,21 +6938,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6972,10 +6962,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>372175</v>
+        <v>372015</v>
       </c>
       <c r="R63" t="n">
-        <v>6934323</v>
+        <v>6934298</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,10 +7024,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122960569</v>
+        <v>122964107</v>
       </c>
       <c r="B64" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7074,10 +7064,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>372015</v>
+        <v>372305</v>
       </c>
       <c r="R64" t="n">
-        <v>6934298</v>
+        <v>6934147</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,10 +7126,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122964992</v>
+        <v>122962156</v>
       </c>
       <c r="B65" t="n">
-        <v>74863</v>
+        <v>90973</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7152,21 +7142,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7176,10 +7166,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>372465</v>
+        <v>372213</v>
       </c>
       <c r="R65" t="n">
-        <v>6934107</v>
+        <v>6934190</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7228,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122966267</v>
+        <v>122970429</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7274,14 +7264,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>372606</v>
+        <v>372253</v>
       </c>
       <c r="R66" t="n">
-        <v>6934099</v>
+        <v>6934293</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,10 +7330,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122969914</v>
+        <v>122967574</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7356,37 +7346,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>372129</v>
+        <v>372536</v>
       </c>
       <c r="R67" t="n">
-        <v>6934375</v>
+        <v>6934127</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7442,10 +7437,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122968306</v>
+        <v>122970638</v>
       </c>
       <c r="B68" t="n">
-        <v>82553</v>
+        <v>57481</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7458,37 +7453,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>372375</v>
+        <v>372342</v>
       </c>
       <c r="R68" t="n">
-        <v>6934215</v>
+        <v>6934292</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122961461</v>
+        <v>122970239</v>
       </c>
       <c r="B2" t="n">
         <v>74866</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372167</v>
+        <v>372139</v>
       </c>
       <c r="R2" t="n">
-        <v>6934263</v>
+        <v>6934344</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122961144</v>
+        <v>122969637</v>
       </c>
       <c r="B3" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372056</v>
+        <v>372139</v>
       </c>
       <c r="R3" t="n">
-        <v>6934270</v>
+        <v>6934367</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122970143</v>
+        <v>122961215</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372099</v>
+        <v>372104</v>
       </c>
       <c r="R4" t="n">
-        <v>6934362</v>
+        <v>6934254</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122969444</v>
+        <v>122969101</v>
       </c>
       <c r="B5" t="n">
-        <v>90973</v>
+        <v>74866</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372175</v>
+        <v>372244</v>
       </c>
       <c r="R5" t="n">
-        <v>6934323</v>
+        <v>6934274</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122965016</v>
+        <v>122960569</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372465</v>
+        <v>372015</v>
       </c>
       <c r="R6" t="n">
-        <v>6934107</v>
+        <v>6934298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122968306</v>
+        <v>122965272</v>
       </c>
       <c r="B7" t="n">
-        <v>82556</v>
+        <v>74866</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372375</v>
+        <v>372519</v>
       </c>
       <c r="R7" t="n">
-        <v>6934215</v>
+        <v>6934058</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122969101</v>
+        <v>122968318</v>
       </c>
       <c r="B8" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372244</v>
+        <v>372375</v>
       </c>
       <c r="R8" t="n">
-        <v>6934274</v>
+        <v>6934215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122968248</v>
+        <v>122965141</v>
       </c>
       <c r="B9" t="n">
-        <v>90951</v>
+        <v>78771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372404</v>
+        <v>372528</v>
       </c>
       <c r="R9" t="n">
-        <v>6934224</v>
+        <v>6934080</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122970155</v>
+        <v>122961601</v>
       </c>
       <c r="B10" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372059</v>
+        <v>372194</v>
       </c>
       <c r="R10" t="n">
-        <v>6934345</v>
+        <v>6934243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122967646</v>
+        <v>122970500</v>
       </c>
       <c r="B11" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372519</v>
+        <v>372318</v>
       </c>
       <c r="R11" t="n">
-        <v>6934145</v>
+        <v>6934300</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122969275</v>
+        <v>122965746</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>74866</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372204</v>
+        <v>372716</v>
       </c>
       <c r="R12" t="n">
-        <v>6934300</v>
+        <v>6934036</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122970193</v>
+        <v>122968399</v>
       </c>
       <c r="B13" t="n">
-        <v>90951</v>
+        <v>79881</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372119</v>
+        <v>372360</v>
       </c>
       <c r="R13" t="n">
-        <v>6934355</v>
+        <v>6934228</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122965746</v>
+        <v>122961461</v>
       </c>
       <c r="B14" t="n">
         <v>74866</v>
@@ -1935,14 +1935,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372716</v>
+        <v>372167</v>
       </c>
       <c r="R14" t="n">
-        <v>6934036</v>
+        <v>6934263</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122968171</v>
+        <v>122970638</v>
       </c>
       <c r="B15" t="n">
-        <v>74866</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,37 +2017,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372420</v>
+        <v>372342</v>
       </c>
       <c r="R15" t="n">
-        <v>6934199</v>
+        <v>6934292</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122970500</v>
+        <v>122967390</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372318</v>
+        <v>372563</v>
       </c>
       <c r="R16" t="n">
-        <v>6934300</v>
+        <v>6934123</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122963972</v>
+        <v>122963945</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>74866</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2307,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122960937</v>
+        <v>122968248</v>
       </c>
       <c r="B18" t="n">
-        <v>78769</v>
+        <v>90953</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>372056</v>
+        <v>372404</v>
       </c>
       <c r="R18" t="n">
-        <v>6934270</v>
+        <v>6934224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122968312</v>
+        <v>122967699</v>
       </c>
       <c r="B19" t="n">
-        <v>74866</v>
+        <v>90975</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>372375</v>
+        <v>372504</v>
       </c>
       <c r="R19" t="n">
-        <v>6934215</v>
+        <v>6934172</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122967925</v>
+        <v>122970659</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,14 +2552,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>372457</v>
+        <v>372348</v>
       </c>
       <c r="R20" t="n">
-        <v>6934206</v>
+        <v>6934275</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122966267</v>
+        <v>122969275</v>
       </c>
       <c r="B21" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>372606</v>
+        <v>372204</v>
       </c>
       <c r="R21" t="n">
-        <v>6934099</v>
+        <v>6934300</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122965816</v>
+        <v>122965907</v>
       </c>
       <c r="B22" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>372684</v>
+        <v>372645</v>
       </c>
       <c r="R22" t="n">
-        <v>6934056</v>
+        <v>6934077</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122965070</v>
+        <v>122961144</v>
       </c>
       <c r="B23" t="n">
-        <v>57481</v>
+        <v>74866</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,42 +2838,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>372491</v>
+        <v>372056</v>
       </c>
       <c r="R23" t="n">
-        <v>6934104</v>
+        <v>6934270</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122969456</v>
+        <v>122964992</v>
       </c>
       <c r="B24" t="n">
         <v>74866</v>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>372175</v>
+        <v>372465</v>
       </c>
       <c r="R24" t="n">
-        <v>6934323</v>
+        <v>6934107</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122967699</v>
+        <v>122968312</v>
       </c>
       <c r="B25" t="n">
-        <v>90973</v>
+        <v>74866</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>372504</v>
+        <v>372375</v>
       </c>
       <c r="R25" t="n">
-        <v>6934172</v>
+        <v>6934215</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122961339</v>
+        <v>122968171</v>
       </c>
       <c r="B26" t="n">
-        <v>78769</v>
+        <v>74866</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>372139</v>
+        <v>372420</v>
       </c>
       <c r="R26" t="n">
-        <v>6934261</v>
+        <v>6934199</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122965907</v>
+        <v>122960937</v>
       </c>
       <c r="B27" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,14 +3266,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>372645</v>
+        <v>372056</v>
       </c>
       <c r="R27" t="n">
-        <v>6934077</v>
+        <v>6934270</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122962287</v>
+        <v>122969120</v>
       </c>
       <c r="B28" t="n">
-        <v>57592</v>
+        <v>78771</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,25 +3344,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>372237</v>
+        <v>372226</v>
       </c>
       <c r="R28" t="n">
-        <v>6934196</v>
+        <v>6934263</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122968061</v>
+        <v>122970143</v>
       </c>
       <c r="B29" t="n">
-        <v>82556</v>
+        <v>78771</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>372448</v>
+        <v>372099</v>
       </c>
       <c r="R29" t="n">
-        <v>6934207</v>
+        <v>6934362</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122967390</v>
+        <v>122970496</v>
       </c>
       <c r="B30" t="n">
-        <v>78769</v>
+        <v>90975</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,21 +3552,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>372563</v>
+        <v>372318</v>
       </c>
       <c r="R30" t="n">
-        <v>6934123</v>
+        <v>6934300</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122967374</v>
+        <v>122968616</v>
       </c>
       <c r="B31" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3654,34 +3654,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>372563</v>
+        <v>372302</v>
       </c>
       <c r="R31" t="n">
-        <v>6934123</v>
+        <v>6934249</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122963945</v>
+        <v>122963595</v>
       </c>
       <c r="B32" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>372274</v>
+        <v>372223</v>
       </c>
       <c r="R32" t="n">
-        <v>6934163</v>
+        <v>6934198</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122964992</v>
+        <v>122965016</v>
       </c>
       <c r="B33" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3947,7 +3947,7 @@
         <v>122968251</v>
       </c>
       <c r="B34" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122965361</v>
+        <v>122968061</v>
       </c>
       <c r="B35" t="n">
-        <v>78769</v>
+        <v>82558</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4062,34 +4062,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>372585</v>
+        <v>372448</v>
       </c>
       <c r="R35" t="n">
-        <v>6934042</v>
+        <v>6934207</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122968966</v>
+        <v>122970429</v>
       </c>
       <c r="B36" t="n">
-        <v>82556</v>
+        <v>78771</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4164,21 +4164,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>372261</v>
+        <v>372253</v>
       </c>
       <c r="R36" t="n">
-        <v>6934264</v>
+        <v>6934293</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122969914</v>
+        <v>122965447</v>
       </c>
       <c r="B37" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4266,37 +4266,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>372129</v>
+        <v>372613</v>
       </c>
       <c r="R37" t="n">
-        <v>6934375</v>
+        <v>6934029</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4352,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122968399</v>
+        <v>122968525</v>
       </c>
       <c r="B38" t="n">
-        <v>79879</v>
+        <v>78771</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4364,25 +4369,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4392,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>372360</v>
+        <v>372330</v>
       </c>
       <c r="R38" t="n">
-        <v>6934228</v>
+        <v>6934242</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4454,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122970239</v>
+        <v>122966267</v>
       </c>
       <c r="B39" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4470,34 +4475,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>372139</v>
+        <v>372606</v>
       </c>
       <c r="R39" t="n">
-        <v>6934344</v>
+        <v>6934099</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4556,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122970659</v>
+        <v>122962156</v>
       </c>
       <c r="B40" t="n">
-        <v>78769</v>
+        <v>90975</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4572,34 +4577,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>372348</v>
+        <v>372213</v>
       </c>
       <c r="R40" t="n">
-        <v>6934275</v>
+        <v>6934190</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4658,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122965141</v>
+        <v>122970713</v>
       </c>
       <c r="B41" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4674,37 +4679,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>372528</v>
+        <v>372362</v>
       </c>
       <c r="R41" t="n">
-        <v>6934080</v>
+        <v>6934267</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4760,10 +4770,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122970496</v>
+        <v>122965816</v>
       </c>
       <c r="B42" t="n">
-        <v>90973</v>
+        <v>74866</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4776,21 +4786,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4800,10 +4810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>372318</v>
+        <v>372684</v>
       </c>
       <c r="R42" t="n">
-        <v>6934300</v>
+        <v>6934056</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4862,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122963587</v>
+        <v>122967574</v>
       </c>
       <c r="B43" t="n">
-        <v>74866</v>
+        <v>57481</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4878,37 +4888,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>372223</v>
+        <v>372536</v>
       </c>
       <c r="R43" t="n">
-        <v>6934198</v>
+        <v>6934127</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4964,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122968129</v>
+        <v>122967646</v>
       </c>
       <c r="B44" t="n">
-        <v>91643</v>
+        <v>78771</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4976,38 +4991,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>372441</v>
+        <v>372519</v>
       </c>
       <c r="R44" t="n">
-        <v>6934188</v>
+        <v>6934145</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5066,10 +5081,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122968525</v>
+        <v>122967925</v>
       </c>
       <c r="B45" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5106,10 +5121,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>372330</v>
+        <v>372457</v>
       </c>
       <c r="R45" t="n">
-        <v>6934242</v>
+        <v>6934206</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5168,10 +5183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122961601</v>
+        <v>122965070</v>
       </c>
       <c r="B46" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5184,37 +5199,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>372194</v>
+        <v>372491</v>
       </c>
       <c r="R46" t="n">
-        <v>6934243</v>
+        <v>6934104</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5270,10 +5290,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122969120</v>
+        <v>122965361</v>
       </c>
       <c r="B47" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5306,14 +5326,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>372226</v>
+        <v>372585</v>
       </c>
       <c r="R47" t="n">
-        <v>6934263</v>
+        <v>6934042</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5372,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122961215</v>
+        <v>122964107</v>
       </c>
       <c r="B48" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5412,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>372104</v>
+        <v>372305</v>
       </c>
       <c r="R48" t="n">
-        <v>6934254</v>
+        <v>6934147</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5474,10 +5494,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122965818</v>
+        <v>122969444</v>
       </c>
       <c r="B49" t="n">
-        <v>78769</v>
+        <v>90975</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5490,34 +5510,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>372684</v>
+        <v>372175</v>
       </c>
       <c r="R49" t="n">
-        <v>6934056</v>
+        <v>6934323</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5576,10 +5596,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122968318</v>
+        <v>122968306</v>
       </c>
       <c r="B50" t="n">
-        <v>78769</v>
+        <v>82558</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5592,21 +5612,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5678,10 +5698,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122970713</v>
+        <v>122969270</v>
       </c>
       <c r="B51" t="n">
-        <v>57481</v>
+        <v>90975</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5694,42 +5714,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>372362</v>
+        <v>372204</v>
       </c>
       <c r="R51" t="n">
-        <v>6934267</v>
+        <v>6934300</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5785,10 +5800,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122968616</v>
+        <v>122967374</v>
       </c>
       <c r="B52" t="n">
-        <v>78769</v>
+        <v>74866</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5801,34 +5816,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>372302</v>
+        <v>372563</v>
       </c>
       <c r="R52" t="n">
-        <v>6934249</v>
+        <v>6934123</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5887,10 +5902,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122963595</v>
+        <v>122968972</v>
       </c>
       <c r="B53" t="n">
-        <v>78769</v>
+        <v>74866</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5903,21 +5918,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5927,10 +5942,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>372223</v>
+        <v>372261</v>
       </c>
       <c r="R53" t="n">
-        <v>6934198</v>
+        <v>6934264</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5989,7 +6004,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122965272</v>
+        <v>122969456</v>
       </c>
       <c r="B54" t="n">
         <v>74866</v>
@@ -6025,14 +6040,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>372519</v>
+        <v>372175</v>
       </c>
       <c r="R54" t="n">
-        <v>6934058</v>
+        <v>6934323</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6091,7 +6106,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122969955</v>
+        <v>122961738</v>
       </c>
       <c r="B55" t="n">
         <v>57481</v>
@@ -6136,10 +6151,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>372131</v>
+        <v>372193</v>
       </c>
       <c r="R55" t="n">
-        <v>6934388</v>
+        <v>6934231</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6198,10 +6213,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122965447</v>
+        <v>122962287</v>
       </c>
       <c r="B56" t="n">
-        <v>57481</v>
+        <v>57592</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6210,20 +6225,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6232,24 +6247,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>372613</v>
+        <v>372237</v>
       </c>
       <c r="R56" t="n">
-        <v>6934029</v>
+        <v>6934196</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6305,10 +6315,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122965564</v>
+        <v>122963972</v>
       </c>
       <c r="B57" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6341,14 +6351,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>372662</v>
+        <v>372274</v>
       </c>
       <c r="R57" t="n">
-        <v>6934028</v>
+        <v>6934163</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6407,10 +6417,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122961588</v>
+        <v>122970193</v>
       </c>
       <c r="B58" t="n">
-        <v>90955</v>
+        <v>90953</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6423,21 +6433,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6447,10 +6457,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>372194</v>
+        <v>372119</v>
       </c>
       <c r="R58" t="n">
-        <v>6934243</v>
+        <v>6934355</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6509,10 +6519,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122969270</v>
+        <v>122969914</v>
       </c>
       <c r="B59" t="n">
-        <v>90973</v>
+        <v>78771</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6525,34 +6535,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>372204</v>
+        <v>372129</v>
       </c>
       <c r="R59" t="n">
-        <v>6934300</v>
+        <v>6934375</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6611,10 +6621,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122961738</v>
+        <v>122961588</v>
       </c>
       <c r="B60" t="n">
-        <v>57481</v>
+        <v>90957</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6627,42 +6637,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>372193</v>
+        <v>372194</v>
       </c>
       <c r="R60" t="n">
-        <v>6934231</v>
+        <v>6934243</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6718,10 +6723,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122968972</v>
+        <v>122968129</v>
       </c>
       <c r="B61" t="n">
-        <v>74866</v>
+        <v>91645</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6730,25 +6735,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,10 +6763,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>372261</v>
+        <v>372441</v>
       </c>
       <c r="R61" t="n">
-        <v>6934264</v>
+        <v>6934188</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6820,10 +6825,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122969637</v>
+        <v>122963587</v>
       </c>
       <c r="B62" t="n">
-        <v>78769</v>
+        <v>74866</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6836,21 +6841,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6860,10 +6865,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>372139</v>
+        <v>372223</v>
       </c>
       <c r="R62" t="n">
-        <v>6934367</v>
+        <v>6934198</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6922,10 +6927,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122960569</v>
+        <v>122965818</v>
       </c>
       <c r="B63" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6958,14 +6963,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>372015</v>
+        <v>372684</v>
       </c>
       <c r="R63" t="n">
-        <v>6934298</v>
+        <v>6934056</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7024,10 +7029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122964107</v>
+        <v>122961339</v>
       </c>
       <c r="B64" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7064,10 +7069,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>372305</v>
+        <v>372139</v>
       </c>
       <c r="R64" t="n">
-        <v>6934147</v>
+        <v>6934261</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7126,10 +7131,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122962156</v>
+        <v>122970155</v>
       </c>
       <c r="B65" t="n">
-        <v>90973</v>
+        <v>78771</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7142,21 +7147,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7166,10 +7171,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>372213</v>
+        <v>372059</v>
       </c>
       <c r="R65" t="n">
-        <v>6934190</v>
+        <v>6934345</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7228,10 +7233,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122970429</v>
+        <v>122969955</v>
       </c>
       <c r="B66" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7244,37 +7249,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>372253</v>
+        <v>372131</v>
       </c>
       <c r="R66" t="n">
-        <v>6934293</v>
+        <v>6934388</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7330,10 +7340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122967574</v>
+        <v>122965564</v>
       </c>
       <c r="B67" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7346,42 +7356,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>372536</v>
+        <v>372662</v>
       </c>
       <c r="R67" t="n">
-        <v>6934127</v>
+        <v>6934028</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7437,10 +7442,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122970638</v>
+        <v>122968966</v>
       </c>
       <c r="B68" t="n">
-        <v>57481</v>
+        <v>82558</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7453,42 +7458,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>372342</v>
+        <v>372261</v>
       </c>
       <c r="R68" t="n">
-        <v>6934292</v>
+        <v>6934264</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122969101</v>
+        <v>122960569</v>
       </c>
       <c r="B5" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372244</v>
+        <v>372015</v>
       </c>
       <c r="R5" t="n">
-        <v>6934274</v>
+        <v>6934298</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122960569</v>
+        <v>122969101</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372015</v>
+        <v>372244</v>
       </c>
       <c r="R6" t="n">
-        <v>6934298</v>
+        <v>6934274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122961461</v>
+        <v>122970638</v>
       </c>
       <c r="B14" t="n">
-        <v>74866</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,37 +1915,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372167</v>
+        <v>372342</v>
       </c>
       <c r="R14" t="n">
-        <v>6934263</v>
+        <v>6934292</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122970638</v>
+        <v>122961461</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>74866</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,42 +2022,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372342</v>
+        <v>372167</v>
       </c>
       <c r="R15" t="n">
-        <v>6934292</v>
+        <v>6934263</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122963945</v>
+        <v>122968248</v>
       </c>
       <c r="B17" t="n">
-        <v>74866</v>
+        <v>90953</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>372274</v>
+        <v>372404</v>
       </c>
       <c r="R17" t="n">
-        <v>6934163</v>
+        <v>6934224</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122968248</v>
+        <v>122967699</v>
       </c>
       <c r="B18" t="n">
-        <v>90953</v>
+        <v>90975</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>372404</v>
+        <v>372504</v>
       </c>
       <c r="R18" t="n">
-        <v>6934224</v>
+        <v>6934172</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122967699</v>
+        <v>122970659</v>
       </c>
       <c r="B19" t="n">
-        <v>90975</v>
+        <v>78771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,34 +2430,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>372504</v>
+        <v>372348</v>
       </c>
       <c r="R19" t="n">
-        <v>6934172</v>
+        <v>6934275</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122970659</v>
+        <v>122969275</v>
       </c>
       <c r="B20" t="n">
         <v>78771</v>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>372348</v>
+        <v>372204</v>
       </c>
       <c r="R20" t="n">
-        <v>6934275</v>
+        <v>6934300</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,7 +2618,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122969275</v>
+        <v>122965907</v>
       </c>
       <c r="B21" t="n">
         <v>78771</v>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>372204</v>
+        <v>372645</v>
       </c>
       <c r="R21" t="n">
-        <v>6934300</v>
+        <v>6934077</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122965907</v>
+        <v>122963945</v>
       </c>
       <c r="B22" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,34 +2736,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>372645</v>
+        <v>372274</v>
       </c>
       <c r="R22" t="n">
-        <v>6934077</v>
+        <v>6934163</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122961144</v>
+        <v>122960937</v>
       </c>
       <c r="B23" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122964992</v>
+        <v>122969120</v>
       </c>
       <c r="B24" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>372465</v>
+        <v>372226</v>
       </c>
       <c r="R24" t="n">
-        <v>6934107</v>
+        <v>6934263</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122968312</v>
+        <v>122970143</v>
       </c>
       <c r="B25" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>372375</v>
+        <v>372099</v>
       </c>
       <c r="R25" t="n">
-        <v>6934215</v>
+        <v>6934362</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122968171</v>
+        <v>122970496</v>
       </c>
       <c r="B26" t="n">
-        <v>74866</v>
+        <v>90975</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,34 +3144,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>372420</v>
+        <v>372318</v>
       </c>
       <c r="R26" t="n">
-        <v>6934199</v>
+        <v>6934300</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122960937</v>
+        <v>122961144</v>
       </c>
       <c r="B27" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122969120</v>
+        <v>122964992</v>
       </c>
       <c r="B28" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,21 +3348,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>372226</v>
+        <v>372465</v>
       </c>
       <c r="R28" t="n">
-        <v>6934263</v>
+        <v>6934107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122970143</v>
+        <v>122968312</v>
       </c>
       <c r="B29" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>372099</v>
+        <v>372375</v>
       </c>
       <c r="R29" t="n">
-        <v>6934362</v>
+        <v>6934215</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122970496</v>
+        <v>122968171</v>
       </c>
       <c r="B30" t="n">
-        <v>90975</v>
+        <v>74866</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,34 +3552,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>372318</v>
+        <v>372420</v>
       </c>
       <c r="R30" t="n">
-        <v>6934300</v>
+        <v>6934199</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122968525</v>
+        <v>122970713</v>
       </c>
       <c r="B38" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4373,37 +4373,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>372330</v>
+        <v>372362</v>
       </c>
       <c r="R38" t="n">
-        <v>6934242</v>
+        <v>6934267</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4459,10 +4464,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122966267</v>
+        <v>122965816</v>
       </c>
       <c r="B39" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4475,21 +4480,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4499,10 +4504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>372606</v>
+        <v>372684</v>
       </c>
       <c r="R39" t="n">
-        <v>6934099</v>
+        <v>6934056</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,10 +4566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122962156</v>
+        <v>122968525</v>
       </c>
       <c r="B40" t="n">
-        <v>90975</v>
+        <v>78771</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4577,21 +4582,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4601,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>372213</v>
+        <v>372330</v>
       </c>
       <c r="R40" t="n">
-        <v>6934190</v>
+        <v>6934242</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,10 +4668,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122970713</v>
+        <v>122966267</v>
       </c>
       <c r="B41" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4679,42 +4684,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>372362</v>
+        <v>372606</v>
       </c>
       <c r="R41" t="n">
-        <v>6934267</v>
+        <v>6934099</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122965816</v>
+        <v>122962156</v>
       </c>
       <c r="B42" t="n">
-        <v>74866</v>
+        <v>90975</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4786,34 +4786,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>372684</v>
+        <v>372213</v>
       </c>
       <c r="R42" t="n">
-        <v>6934056</v>
+        <v>6934190</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5800,10 +5800,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122967374</v>
+        <v>122961738</v>
       </c>
       <c r="B52" t="n">
-        <v>74866</v>
+        <v>57481</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5816,37 +5816,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>372563</v>
+        <v>372193</v>
       </c>
       <c r="R52" t="n">
-        <v>6934123</v>
+        <v>6934231</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5902,7 +5907,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122968972</v>
+        <v>122967374</v>
       </c>
       <c r="B53" t="n">
         <v>74866</v>
@@ -5938,14 +5943,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>372261</v>
+        <v>372563</v>
       </c>
       <c r="R53" t="n">
-        <v>6934264</v>
+        <v>6934123</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6004,7 +6009,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122969456</v>
+        <v>122968972</v>
       </c>
       <c r="B54" t="n">
         <v>74866</v>
@@ -6044,10 +6049,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>372175</v>
+        <v>372261</v>
       </c>
       <c r="R54" t="n">
-        <v>6934323</v>
+        <v>6934264</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6106,10 +6111,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122961738</v>
+        <v>122969456</v>
       </c>
       <c r="B55" t="n">
-        <v>57481</v>
+        <v>74866</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6122,42 +6127,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>372193</v>
+        <v>372175</v>
       </c>
       <c r="R55" t="n">
-        <v>6934231</v>
+        <v>6934323</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122970239</v>
+        <v>122969456</v>
       </c>
       <c r="B2" t="n">
         <v>74866</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372139</v>
+        <v>372175</v>
       </c>
       <c r="R2" t="n">
-        <v>6934344</v>
+        <v>6934323</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122969637</v>
+        <v>122964107</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372139</v>
+        <v>372305</v>
       </c>
       <c r="R3" t="n">
-        <v>6934367</v>
+        <v>6934147</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122961215</v>
+        <v>122969914</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372104</v>
+        <v>372129</v>
       </c>
       <c r="R4" t="n">
-        <v>6934254</v>
+        <v>6934375</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122960569</v>
+        <v>122968966</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>82559</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372015</v>
+        <v>372261</v>
       </c>
       <c r="R5" t="n">
-        <v>6934298</v>
+        <v>6934264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122969101</v>
+        <v>122970638</v>
       </c>
       <c r="B6" t="n">
-        <v>74866</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,37 +1099,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372244</v>
+        <v>372342</v>
       </c>
       <c r="R6" t="n">
-        <v>6934274</v>
+        <v>6934292</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122965272</v>
+        <v>122969120</v>
       </c>
       <c r="B7" t="n">
-        <v>74866</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372519</v>
+        <v>372226</v>
       </c>
       <c r="R7" t="n">
-        <v>6934058</v>
+        <v>6934263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122968318</v>
+        <v>122965070</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1308,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372375</v>
+        <v>372491</v>
       </c>
       <c r="R8" t="n">
-        <v>6934215</v>
+        <v>6934104</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122965141</v>
+        <v>122970193</v>
       </c>
       <c r="B9" t="n">
-        <v>78771</v>
+        <v>90959</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1415,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372528</v>
+        <v>372119</v>
       </c>
       <c r="R9" t="n">
-        <v>6934080</v>
+        <v>6934355</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122961601</v>
+        <v>122970713</v>
       </c>
       <c r="B10" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,37 +1517,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372194</v>
+        <v>372362</v>
       </c>
       <c r="R10" t="n">
-        <v>6934243</v>
+        <v>6934267</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122970500</v>
+        <v>122962287</v>
       </c>
       <c r="B11" t="n">
-        <v>78771</v>
+        <v>57592</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,41 +1620,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372318</v>
+        <v>372237</v>
       </c>
       <c r="R11" t="n">
-        <v>6934300</v>
+        <v>6934196</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122965746</v>
+        <v>122970496</v>
       </c>
       <c r="B12" t="n">
-        <v>74866</v>
+        <v>90981</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372716</v>
+        <v>372318</v>
       </c>
       <c r="R12" t="n">
-        <v>6934036</v>
+        <v>6934300</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122968399</v>
+        <v>122961215</v>
       </c>
       <c r="B13" t="n">
-        <v>79881</v>
+        <v>78772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372360</v>
+        <v>372104</v>
       </c>
       <c r="R13" t="n">
-        <v>6934228</v>
+        <v>6934254</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122970638</v>
+        <v>122970429</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,42 +1930,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372342</v>
+        <v>372253</v>
       </c>
       <c r="R14" t="n">
-        <v>6934292</v>
+        <v>6934293</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122961461</v>
+        <v>122970155</v>
       </c>
       <c r="B15" t="n">
-        <v>74866</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372167</v>
+        <v>372059</v>
       </c>
       <c r="R15" t="n">
-        <v>6934263</v>
+        <v>6934345</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122967390</v>
+        <v>122967699</v>
       </c>
       <c r="B16" t="n">
-        <v>78771</v>
+        <v>90981</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,34 +2134,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372563</v>
+        <v>372504</v>
       </c>
       <c r="R16" t="n">
-        <v>6934123</v>
+        <v>6934172</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122968248</v>
+        <v>122969637</v>
       </c>
       <c r="B17" t="n">
-        <v>90953</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>372404</v>
+        <v>372139</v>
       </c>
       <c r="R17" t="n">
-        <v>6934224</v>
+        <v>6934367</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122967699</v>
+        <v>122965746</v>
       </c>
       <c r="B18" t="n">
-        <v>90975</v>
+        <v>74866</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,34 +2338,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>372504</v>
+        <v>372716</v>
       </c>
       <c r="R18" t="n">
-        <v>6934172</v>
+        <v>6934036</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122970659</v>
+        <v>122968399</v>
       </c>
       <c r="B19" t="n">
-        <v>78771</v>
+        <v>79882</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,38 +2436,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>372348</v>
+        <v>372360</v>
       </c>
       <c r="R19" t="n">
-        <v>6934275</v>
+        <v>6934228</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122969275</v>
+        <v>122961601</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,14 +2562,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>372204</v>
+        <v>372194</v>
       </c>
       <c r="R20" t="n">
-        <v>6934300</v>
+        <v>6934243</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122965907</v>
+        <v>122968171</v>
       </c>
       <c r="B21" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,34 +2644,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>372645</v>
+        <v>372420</v>
       </c>
       <c r="R21" t="n">
-        <v>6934077</v>
+        <v>6934199</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122963945</v>
+        <v>122968061</v>
       </c>
       <c r="B22" t="n">
-        <v>74866</v>
+        <v>82559</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2746,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>372274</v>
+        <v>372448</v>
       </c>
       <c r="R22" t="n">
-        <v>6934163</v>
+        <v>6934207</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122960937</v>
+        <v>122963972</v>
       </c>
       <c r="B23" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>372056</v>
+        <v>372274</v>
       </c>
       <c r="R23" t="n">
-        <v>6934270</v>
+        <v>6934163</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122969120</v>
+        <v>122968525</v>
       </c>
       <c r="B24" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>372226</v>
+        <v>372330</v>
       </c>
       <c r="R24" t="n">
-        <v>6934263</v>
+        <v>6934242</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122970143</v>
+        <v>122969101</v>
       </c>
       <c r="B25" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3052,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>372099</v>
+        <v>372244</v>
       </c>
       <c r="R25" t="n">
-        <v>6934362</v>
+        <v>6934274</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,10 +3138,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122970496</v>
+        <v>122970659</v>
       </c>
       <c r="B26" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3154,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>372318</v>
+        <v>372348</v>
       </c>
       <c r="R26" t="n">
-        <v>6934300</v>
+        <v>6934275</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3332,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122964992</v>
+        <v>122969270</v>
       </c>
       <c r="B28" t="n">
-        <v>74866</v>
+        <v>90981</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,34 +3358,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>372465</v>
+        <v>372204</v>
       </c>
       <c r="R28" t="n">
-        <v>6934107</v>
+        <v>6934300</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122968312</v>
+        <v>122969955</v>
       </c>
       <c r="B29" t="n">
-        <v>74866</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,37 +3460,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>372375</v>
+        <v>372131</v>
       </c>
       <c r="R29" t="n">
-        <v>6934215</v>
+        <v>6934388</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3536,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122968171</v>
+        <v>122967646</v>
       </c>
       <c r="B30" t="n">
-        <v>74866</v>
+        <v>78772</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,34 +3567,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>372420</v>
+        <v>372519</v>
       </c>
       <c r="R30" t="n">
-        <v>6934199</v>
+        <v>6934145</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,10 +3653,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122968616</v>
+        <v>122966267</v>
       </c>
       <c r="B31" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3674,14 +3689,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>372302</v>
+        <v>372606</v>
       </c>
       <c r="R31" t="n">
-        <v>6934249</v>
+        <v>6934099</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122963595</v>
+        <v>122967374</v>
       </c>
       <c r="B32" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3756,34 +3771,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>372223</v>
+        <v>372563</v>
       </c>
       <c r="R32" t="n">
-        <v>6934198</v>
+        <v>6934123</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122965016</v>
+        <v>122963945</v>
       </c>
       <c r="B33" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3858,21 +3873,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3882,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>372465</v>
+        <v>372274</v>
       </c>
       <c r="R33" t="n">
-        <v>6934107</v>
+        <v>6934163</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3944,10 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122968251</v>
+        <v>122961588</v>
       </c>
       <c r="B34" t="n">
-        <v>78771</v>
+        <v>90963</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3960,21 +3975,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3984,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>372404</v>
+        <v>372194</v>
       </c>
       <c r="R34" t="n">
-        <v>6934224</v>
+        <v>6934243</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4046,10 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122968061</v>
+        <v>122968312</v>
       </c>
       <c r="B35" t="n">
-        <v>82558</v>
+        <v>74866</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4062,21 +4077,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4086,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>372448</v>
+        <v>372375</v>
       </c>
       <c r="R35" t="n">
-        <v>6934207</v>
+        <v>6934215</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4148,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122970429</v>
+        <v>122968251</v>
       </c>
       <c r="B36" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4188,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>372253</v>
+        <v>372404</v>
       </c>
       <c r="R36" t="n">
-        <v>6934293</v>
+        <v>6934224</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4250,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122965447</v>
+        <v>122969275</v>
       </c>
       <c r="B37" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4266,42 +4281,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>372613</v>
+        <v>372204</v>
       </c>
       <c r="R37" t="n">
-        <v>6934029</v>
+        <v>6934300</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4357,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122970713</v>
+        <v>122963587</v>
       </c>
       <c r="B38" t="n">
-        <v>57481</v>
+        <v>74866</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4373,42 +4383,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>372362</v>
+        <v>372223</v>
       </c>
       <c r="R38" t="n">
-        <v>6934267</v>
+        <v>6934198</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4464,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122965816</v>
+        <v>122960937</v>
       </c>
       <c r="B39" t="n">
-        <v>74866</v>
+        <v>78772</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4480,34 +4485,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>372684</v>
+        <v>372056</v>
       </c>
       <c r="R39" t="n">
-        <v>6934056</v>
+        <v>6934270</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122968525</v>
+        <v>122960569</v>
       </c>
       <c r="B40" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>372330</v>
+        <v>372015</v>
       </c>
       <c r="R40" t="n">
-        <v>6934242</v>
+        <v>6934298</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4668,10 +4673,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122966267</v>
+        <v>122964992</v>
       </c>
       <c r="B41" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4684,34 +4689,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>372606</v>
+        <v>372465</v>
       </c>
       <c r="R41" t="n">
-        <v>6934099</v>
+        <v>6934107</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,10 +4775,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122962156</v>
+        <v>122970500</v>
       </c>
       <c r="B42" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4786,34 +4791,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>372213</v>
+        <v>372318</v>
       </c>
       <c r="R42" t="n">
-        <v>6934190</v>
+        <v>6934300</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4872,10 +4877,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122967574</v>
+        <v>122968129</v>
       </c>
       <c r="B43" t="n">
-        <v>57481</v>
+        <v>91651</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4884,46 +4889,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>372536</v>
+        <v>372441</v>
       </c>
       <c r="R43" t="n">
-        <v>6934127</v>
+        <v>6934188</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4979,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122967646</v>
+        <v>122962156</v>
       </c>
       <c r="B44" t="n">
-        <v>78771</v>
+        <v>90981</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,34 +4995,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>372519</v>
+        <v>372213</v>
       </c>
       <c r="R44" t="n">
-        <v>6934145</v>
+        <v>6934190</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5081,10 +5081,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122967925</v>
+        <v>122965564</v>
       </c>
       <c r="B45" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5117,14 +5117,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>372457</v>
+        <v>372662</v>
       </c>
       <c r="R45" t="n">
-        <v>6934206</v>
+        <v>6934028</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,10 +5183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122965070</v>
+        <v>122965818</v>
       </c>
       <c r="B46" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,42 +5199,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>372491</v>
+        <v>372684</v>
       </c>
       <c r="R46" t="n">
-        <v>6934104</v>
+        <v>6934056</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5290,10 +5285,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122965361</v>
+        <v>122965907</v>
       </c>
       <c r="B47" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5330,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>372585</v>
+        <v>372645</v>
       </c>
       <c r="R47" t="n">
-        <v>6934042</v>
+        <v>6934077</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122964107</v>
+        <v>122970239</v>
       </c>
       <c r="B48" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5408,21 +5403,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5432,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>372305</v>
+        <v>372139</v>
       </c>
       <c r="R48" t="n">
-        <v>6934147</v>
+        <v>6934344</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122969444</v>
+        <v>122967390</v>
       </c>
       <c r="B49" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5510,34 +5505,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>372175</v>
+        <v>372563</v>
       </c>
       <c r="R49" t="n">
-        <v>6934323</v>
+        <v>6934123</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5596,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122968306</v>
+        <v>122969444</v>
       </c>
       <c r="B50" t="n">
-        <v>82558</v>
+        <v>90981</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5612,21 +5607,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5636,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>372375</v>
+        <v>372175</v>
       </c>
       <c r="R50" t="n">
-        <v>6934215</v>
+        <v>6934323</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5698,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122969270</v>
+        <v>122965361</v>
       </c>
       <c r="B51" t="n">
-        <v>90975</v>
+        <v>78772</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5714,21 +5709,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5738,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>372204</v>
+        <v>372585</v>
       </c>
       <c r="R51" t="n">
-        <v>6934300</v>
+        <v>6934042</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5800,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122961738</v>
+        <v>122961339</v>
       </c>
       <c r="B52" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5816,42 +5811,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>372193</v>
+        <v>372139</v>
       </c>
       <c r="R52" t="n">
-        <v>6934231</v>
+        <v>6934261</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5907,7 +5897,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122967374</v>
+        <v>122965272</v>
       </c>
       <c r="B53" t="n">
         <v>74866</v>
@@ -5947,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>372563</v>
+        <v>372519</v>
       </c>
       <c r="R53" t="n">
-        <v>6934123</v>
+        <v>6934058</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6009,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122968972</v>
+        <v>122968616</v>
       </c>
       <c r="B54" t="n">
-        <v>74866</v>
+        <v>78772</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6025,21 +6015,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6049,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>372261</v>
+        <v>372302</v>
       </c>
       <c r="R54" t="n">
-        <v>6934264</v>
+        <v>6934249</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6111,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122969456</v>
+        <v>122970143</v>
       </c>
       <c r="B55" t="n">
-        <v>74866</v>
+        <v>78772</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6127,21 +6117,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6151,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>372175</v>
+        <v>372099</v>
       </c>
       <c r="R55" t="n">
-        <v>6934323</v>
+        <v>6934362</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6213,10 +6203,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122962287</v>
+        <v>122965447</v>
       </c>
       <c r="B56" t="n">
-        <v>57592</v>
+        <v>57481</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6225,20 +6215,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6247,19 +6237,24 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>372237</v>
+        <v>372613</v>
       </c>
       <c r="R56" t="n">
-        <v>6934196</v>
+        <v>6934029</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6315,10 +6310,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122963972</v>
+        <v>122967574</v>
       </c>
       <c r="B57" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6331,37 +6326,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>372274</v>
+        <v>372536</v>
       </c>
       <c r="R57" t="n">
-        <v>6934163</v>
+        <v>6934127</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6417,10 +6417,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122970193</v>
+        <v>122968248</v>
       </c>
       <c r="B58" t="n">
-        <v>90953</v>
+        <v>90959</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>372119</v>
+        <v>372404</v>
       </c>
       <c r="R58" t="n">
-        <v>6934355</v>
+        <v>6934224</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,10 +6519,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122969914</v>
+        <v>122965016</v>
       </c>
       <c r="B59" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>372129</v>
+        <v>372465</v>
       </c>
       <c r="R59" t="n">
-        <v>6934375</v>
+        <v>6934107</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6621,10 +6621,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122961588</v>
+        <v>122965816</v>
       </c>
       <c r="B60" t="n">
-        <v>90957</v>
+        <v>74866</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6637,34 +6637,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>372194</v>
+        <v>372684</v>
       </c>
       <c r="R60" t="n">
-        <v>6934243</v>
+        <v>6934056</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,10 +6723,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122968129</v>
+        <v>122967925</v>
       </c>
       <c r="B61" t="n">
-        <v>91645</v>
+        <v>78772</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6735,25 +6735,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>372441</v>
+        <v>372457</v>
       </c>
       <c r="R61" t="n">
-        <v>6934188</v>
+        <v>6934206</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6825,7 +6825,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122963587</v>
+        <v>122968972</v>
       </c>
       <c r="B62" t="n">
         <v>74866</v>
@@ -6865,10 +6865,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>372223</v>
+        <v>372261</v>
       </c>
       <c r="R62" t="n">
-        <v>6934198</v>
+        <v>6934264</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122965818</v>
+        <v>122961738</v>
       </c>
       <c r="B63" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6943,37 +6943,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>372684</v>
+        <v>372193</v>
       </c>
       <c r="R63" t="n">
-        <v>6934056</v>
+        <v>6934231</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7029,10 +7034,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122961339</v>
+        <v>122968306</v>
       </c>
       <c r="B64" t="n">
-        <v>78771</v>
+        <v>82559</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7045,21 +7050,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7069,10 +7074,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>372139</v>
+        <v>372375</v>
       </c>
       <c r="R64" t="n">
-        <v>6934261</v>
+        <v>6934215</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7131,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122970155</v>
+        <v>122963595</v>
       </c>
       <c r="B65" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7171,10 +7176,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>372059</v>
+        <v>372223</v>
       </c>
       <c r="R65" t="n">
-        <v>6934345</v>
+        <v>6934198</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7233,10 +7238,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122969955</v>
+        <v>122965141</v>
       </c>
       <c r="B66" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7249,42 +7254,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>372131</v>
+        <v>372528</v>
       </c>
       <c r="R66" t="n">
-        <v>6934388</v>
+        <v>6934080</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122965564</v>
+        <v>122961461</v>
       </c>
       <c r="B67" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7356,34 +7356,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>372662</v>
+        <v>372167</v>
       </c>
       <c r="R67" t="n">
-        <v>6934028</v>
+        <v>6934263</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122968966</v>
+        <v>122968318</v>
       </c>
       <c r="B68" t="n">
-        <v>82558</v>
+        <v>78772</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7458,21 +7458,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>372261</v>
+        <v>372375</v>
       </c>
       <c r="R68" t="n">
-        <v>6934264</v>
+        <v>6934215</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122965746</v>
+        <v>122969270</v>
       </c>
       <c r="B26" t="n">
-        <v>74869</v>
+        <v>90984</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>372716</v>
+        <v>372204</v>
       </c>
       <c r="R26" t="n">
-        <v>6934036</v>
+        <v>6934300</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122968399</v>
+        <v>122968312</v>
       </c>
       <c r="B27" t="n">
-        <v>79885</v>
+        <v>74869</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3247,25 +3247,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>372360</v>
+        <v>372375</v>
       </c>
       <c r="R27" t="n">
-        <v>6934228</v>
+        <v>6934215</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122963945</v>
+        <v>122969637</v>
       </c>
       <c r="B28" t="n">
-        <v>74869</v>
+        <v>78775</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>372274</v>
+        <v>372139</v>
       </c>
       <c r="R28" t="n">
-        <v>6934163</v>
+        <v>6934367</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122969270</v>
+        <v>122963972</v>
       </c>
       <c r="B29" t="n">
-        <v>90984</v>
+        <v>78775</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,34 +3455,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>372204</v>
+        <v>372274</v>
       </c>
       <c r="R29" t="n">
-        <v>6934300</v>
+        <v>6934163</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122968312</v>
+        <v>122965818</v>
       </c>
       <c r="B30" t="n">
-        <v>74869</v>
+        <v>78775</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,34 +3557,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>372375</v>
+        <v>372684</v>
       </c>
       <c r="R30" t="n">
-        <v>6934215</v>
+        <v>6934056</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122969637</v>
+        <v>122965746</v>
       </c>
       <c r="B31" t="n">
-        <v>78775</v>
+        <v>74869</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,34 +3659,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>372139</v>
+        <v>372716</v>
       </c>
       <c r="R31" t="n">
-        <v>6934367</v>
+        <v>6934036</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122963972</v>
+        <v>122968399</v>
       </c>
       <c r="B32" t="n">
-        <v>78775</v>
+        <v>79885</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3757,25 +3757,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>372274</v>
+        <v>372360</v>
       </c>
       <c r="R32" t="n">
-        <v>6934163</v>
+        <v>6934228</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122965818</v>
+        <v>122963945</v>
       </c>
       <c r="B33" t="n">
-        <v>78775</v>
+        <v>74869</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,34 +3863,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>372684</v>
+        <v>372274</v>
       </c>
       <c r="R33" t="n">
-        <v>6934056</v>
+        <v>6934163</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -6825,10 +6825,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122968248</v>
+        <v>122965447</v>
       </c>
       <c r="B62" t="n">
-        <v>90962</v>
+        <v>57481</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6841,37 +6841,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>372404</v>
+        <v>372613</v>
       </c>
       <c r="R62" t="n">
-        <v>6934224</v>
+        <v>6934029</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6927,10 +6932,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122968251</v>
+        <v>122968248</v>
       </c>
       <c r="B63" t="n">
-        <v>78775</v>
+        <v>90962</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6943,21 +6948,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7029,7 +7034,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122960569</v>
+        <v>122968251</v>
       </c>
       <c r="B64" t="n">
         <v>78775</v>
@@ -7069,10 +7074,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>372015</v>
+        <v>372404</v>
       </c>
       <c r="R64" t="n">
-        <v>6934298</v>
+        <v>6934224</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7131,10 +7136,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122965447</v>
+        <v>122960569</v>
       </c>
       <c r="B65" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7147,42 +7152,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>372613</v>
+        <v>372015</v>
       </c>
       <c r="R65" t="n">
-        <v>6934029</v>
+        <v>6934298</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>

--- a/artfynd/A 5780-2025 artfynd.xlsx
+++ b/artfynd/A 5780-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122961601</v>
+        <v>122967646</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372194</v>
+        <v>372519</v>
       </c>
       <c r="R2" t="n">
-        <v>6934243</v>
+        <v>6934145</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122962287</v>
+        <v>122970429</v>
       </c>
       <c r="B3" t="n">
-        <v>57592</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372237</v>
+        <v>372253</v>
       </c>
       <c r="R3" t="n">
-        <v>6934196</v>
+        <v>6934293</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122970496</v>
+        <v>122961461</v>
       </c>
       <c r="B4" t="n">
-        <v>90984</v>
+        <v>74875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372318</v>
+        <v>372167</v>
       </c>
       <c r="R4" t="n">
-        <v>6934300</v>
+        <v>6934263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122965361</v>
+        <v>122969456</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>74875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372585</v>
+        <v>372175</v>
       </c>
       <c r="R5" t="n">
-        <v>6934042</v>
+        <v>6934323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122965272</v>
+        <v>122968966</v>
       </c>
       <c r="B6" t="n">
-        <v>74869</v>
+        <v>82568</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372519</v>
+        <v>372261</v>
       </c>
       <c r="R6" t="n">
-        <v>6934058</v>
+        <v>6934264</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122964107</v>
+        <v>122970239</v>
       </c>
       <c r="B7" t="n">
-        <v>78775</v>
+        <v>74875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372305</v>
+        <v>372139</v>
       </c>
       <c r="R7" t="n">
-        <v>6934147</v>
+        <v>6934344</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122961339</v>
+        <v>122968061</v>
       </c>
       <c r="B8" t="n">
-        <v>78775</v>
+        <v>82568</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372139</v>
+        <v>372448</v>
       </c>
       <c r="R8" t="n">
-        <v>6934261</v>
+        <v>6934207</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122966267</v>
+        <v>122968171</v>
       </c>
       <c r="B9" t="n">
-        <v>78775</v>
+        <v>74875</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372606</v>
+        <v>372420</v>
       </c>
       <c r="R9" t="n">
-        <v>6934099</v>
+        <v>6934199</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122968318</v>
+        <v>122970143</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372375</v>
+        <v>372099</v>
       </c>
       <c r="R10" t="n">
-        <v>6934215</v>
+        <v>6934362</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122965564</v>
+        <v>122960569</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,14 +1629,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372662</v>
+        <v>372015</v>
       </c>
       <c r="R11" t="n">
-        <v>6934028</v>
+        <v>6934298</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122967925</v>
+        <v>122970193</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>90979</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372457</v>
+        <v>372119</v>
       </c>
       <c r="R12" t="n">
-        <v>6934206</v>
+        <v>6934355</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122965907</v>
+        <v>122969914</v>
       </c>
       <c r="B13" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,14 +1833,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372645</v>
+        <v>372129</v>
       </c>
       <c r="R13" t="n">
-        <v>6934077</v>
+        <v>6934375</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122970239</v>
+        <v>122968129</v>
       </c>
       <c r="B14" t="n">
-        <v>74869</v>
+        <v>91671</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372139</v>
+        <v>372441</v>
       </c>
       <c r="R14" t="n">
-        <v>6934344</v>
+        <v>6934188</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122970638</v>
+        <v>122961339</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,42 +2017,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372342</v>
+        <v>372139</v>
       </c>
       <c r="R15" t="n">
-        <v>6934292</v>
+        <v>6934261</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122968061</v>
+        <v>122965907</v>
       </c>
       <c r="B16" t="n">
-        <v>82562</v>
+        <v>78781</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,34 +2119,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372448</v>
+        <v>372645</v>
       </c>
       <c r="R16" t="n">
-        <v>6934207</v>
+        <v>6934077</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122969120</v>
+        <v>122970713</v>
       </c>
       <c r="B17" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,37 +2221,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>372226</v>
+        <v>372362</v>
       </c>
       <c r="R17" t="n">
-        <v>6934263</v>
+        <v>6934267</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122965016</v>
+        <v>122965564</v>
       </c>
       <c r="B18" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,14 +2348,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>372465</v>
+        <v>372662</v>
       </c>
       <c r="R18" t="n">
-        <v>6934107</v>
+        <v>6934028</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122965816</v>
+        <v>122961144</v>
       </c>
       <c r="B19" t="n">
-        <v>74869</v>
+        <v>74875</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,14 +2450,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>372684</v>
+        <v>372056</v>
       </c>
       <c r="R19" t="n">
-        <v>6934056</v>
+        <v>6934270</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122967646</v>
+        <v>122961588</v>
       </c>
       <c r="B20" t="n">
-        <v>78775</v>
+        <v>90983</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,34 +2532,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>372519</v>
+        <v>372194</v>
       </c>
       <c r="R20" t="n">
-        <v>6934145</v>
+        <v>6934243</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122970500</v>
+        <v>122967390</v>
       </c>
       <c r="B21" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>372318</v>
+        <v>372563</v>
       </c>
       <c r="R21" t="n">
-        <v>6934300</v>
+        <v>6934123</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122969444</v>
+        <v>122965746</v>
       </c>
       <c r="B22" t="n">
-        <v>90984</v>
+        <v>74875</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,34 +2736,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>372175</v>
+        <v>372716</v>
       </c>
       <c r="R22" t="n">
-        <v>6934323</v>
+        <v>6934036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122968306</v>
+        <v>122964107</v>
       </c>
       <c r="B23" t="n">
-        <v>82562</v>
+        <v>78781</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>372375</v>
+        <v>372305</v>
       </c>
       <c r="R23" t="n">
-        <v>6934215</v>
+        <v>6934147</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122961215</v>
+        <v>122966267</v>
       </c>
       <c r="B24" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,14 +2960,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>372104</v>
+        <v>372606</v>
       </c>
       <c r="R24" t="n">
-        <v>6934254</v>
+        <v>6934099</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122969955</v>
+        <v>122962287</v>
       </c>
       <c r="B25" t="n">
-        <v>57481</v>
+        <v>57598</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,20 +3038,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3060,24 +3060,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>372131</v>
+        <v>372237</v>
       </c>
       <c r="R25" t="n">
-        <v>6934388</v>
+        <v>6934196</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3133,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122969270</v>
+        <v>122961738</v>
       </c>
       <c r="B26" t="n">
-        <v>90984</v>
+        <v>57487</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,37 +3144,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>372204</v>
+        <v>372193</v>
       </c>
       <c r="R26" t="n">
-        <v>6934300</v>
+        <v>6934231</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122968312</v>
+        <v>122963595</v>
       </c>
       <c r="B27" t="n">
-        <v>74869</v>
+        <v>78781</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>372375</v>
+        <v>372223</v>
       </c>
       <c r="R27" t="n">
-        <v>6934215</v>
+        <v>6934198</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122969637</v>
+        <v>122967699</v>
       </c>
       <c r="B28" t="n">
-        <v>78775</v>
+        <v>91001</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>372139</v>
+        <v>372504</v>
       </c>
       <c r="R28" t="n">
-        <v>6934367</v>
+        <v>6934172</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122963972</v>
+        <v>122968248</v>
       </c>
       <c r="B29" t="n">
-        <v>78775</v>
+        <v>90979</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>372274</v>
+        <v>372404</v>
       </c>
       <c r="R29" t="n">
-        <v>6934163</v>
+        <v>6934224</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122965818</v>
+        <v>122968251</v>
       </c>
       <c r="B30" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3577,14 +3577,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>372684</v>
+        <v>372404</v>
       </c>
       <c r="R30" t="n">
-        <v>6934056</v>
+        <v>6934224</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122965746</v>
+        <v>122967925</v>
       </c>
       <c r="B31" t="n">
-        <v>74869</v>
+        <v>78781</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,34 +3659,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>372716</v>
+        <v>372457</v>
       </c>
       <c r="R31" t="n">
-        <v>6934036</v>
+        <v>6934206</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
         <v>122968399</v>
       </c>
       <c r="B32" t="n">
-        <v>79885</v>
+        <v>79891</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122963945</v>
+        <v>122969101</v>
       </c>
       <c r="B33" t="n">
-        <v>74869</v>
+        <v>74875</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>372274</v>
+        <v>372244</v>
       </c>
       <c r="R33" t="n">
-        <v>6934163</v>
+        <v>6934274</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122968129</v>
+        <v>122967574</v>
       </c>
       <c r="B34" t="n">
-        <v>91654</v>
+        <v>57487</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3961,41 +3961,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>372441</v>
+        <v>372536</v>
       </c>
       <c r="R34" t="n">
-        <v>6934188</v>
+        <v>6934127</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4051,10 +4056,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122970193</v>
+        <v>122961601</v>
       </c>
       <c r="B35" t="n">
-        <v>90962</v>
+        <v>78781</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4067,21 +4072,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,10 +4096,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>372119</v>
+        <v>372194</v>
       </c>
       <c r="R35" t="n">
-        <v>6934355</v>
+        <v>6934243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,10 +4158,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122968966</v>
+        <v>122964992</v>
       </c>
       <c r="B36" t="n">
-        <v>82562</v>
+        <v>74875</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4169,21 +4174,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4193,10 +4198,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>372261</v>
+        <v>372465</v>
       </c>
       <c r="R36" t="n">
-        <v>6934264</v>
+        <v>6934107</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,10 +4260,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122969456</v>
+        <v>122969120</v>
       </c>
       <c r="B37" t="n">
-        <v>74869</v>
+        <v>78781</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4271,21 +4276,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4295,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>372175</v>
+        <v>372226</v>
       </c>
       <c r="R37" t="n">
-        <v>6934323</v>
+        <v>6934263</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4357,10 +4362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122965141</v>
+        <v>122963945</v>
       </c>
       <c r="B38" t="n">
-        <v>78775</v>
+        <v>74875</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4373,34 +4378,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>372528</v>
+        <v>372274</v>
       </c>
       <c r="R38" t="n">
-        <v>6934080</v>
+        <v>6934163</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4459,10 +4464,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122969914</v>
+        <v>122970500</v>
       </c>
       <c r="B39" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4495,14 +4500,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>372129</v>
+        <v>372318</v>
       </c>
       <c r="R39" t="n">
-        <v>6934375</v>
+        <v>6934300</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,10 +4566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122968171</v>
+        <v>122965818</v>
       </c>
       <c r="B40" t="n">
-        <v>74869</v>
+        <v>78781</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4577,34 +4582,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>372420</v>
+        <v>372684</v>
       </c>
       <c r="R40" t="n">
-        <v>6934199</v>
+        <v>6934056</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,10 +4668,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122967574</v>
+        <v>122965816</v>
       </c>
       <c r="B41" t="n">
-        <v>57481</v>
+        <v>74875</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4679,42 +4684,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>372536</v>
+        <v>372684</v>
       </c>
       <c r="R41" t="n">
-        <v>6934127</v>
+        <v>6934056</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122970713</v>
+        <v>122970496</v>
       </c>
       <c r="B42" t="n">
-        <v>57481</v>
+        <v>91001</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4786,42 +4786,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>372362</v>
+        <v>372318</v>
       </c>
       <c r="R42" t="n">
-        <v>6934267</v>
+        <v>6934300</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4877,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122968525</v>
+        <v>122967374</v>
       </c>
       <c r="B43" t="n">
-        <v>78775</v>
+        <v>74875</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4893,34 +4888,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>372330</v>
+        <v>372563</v>
       </c>
       <c r="R43" t="n">
-        <v>6934242</v>
+        <v>6934123</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4979,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122963587</v>
+        <v>122969270</v>
       </c>
       <c r="B44" t="n">
-        <v>74869</v>
+        <v>91001</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,34 +4990,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>372223</v>
+        <v>372204</v>
       </c>
       <c r="R44" t="n">
-        <v>6934198</v>
+        <v>6934300</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5081,10 +5076,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122961738</v>
+        <v>122965361</v>
       </c>
       <c r="B45" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,42 +5092,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>372193</v>
+        <v>372585</v>
       </c>
       <c r="R45" t="n">
-        <v>6934231</v>
+        <v>6934042</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5188,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122962156</v>
+        <v>122968525</v>
       </c>
       <c r="B46" t="n">
-        <v>90984</v>
+        <v>78781</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5204,21 +5194,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5228,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>372213</v>
+        <v>372330</v>
       </c>
       <c r="R46" t="n">
-        <v>6934190</v>
+        <v>6934242</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122961588</v>
+        <v>122965141</v>
       </c>
       <c r="B47" t="n">
-        <v>90966</v>
+        <v>78781</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5306,34 +5296,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>372194</v>
+        <v>372528</v>
       </c>
       <c r="R47" t="n">
-        <v>6934243</v>
+        <v>6934080</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,10 +5382,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122969275</v>
+        <v>122961215</v>
       </c>
       <c r="B48" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5428,14 +5418,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>372204</v>
+        <v>372104</v>
       </c>
       <c r="R48" t="n">
-        <v>6934300</v>
+        <v>6934254</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5497,7 +5487,7 @@
         <v>122970155</v>
       </c>
       <c r="B49" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5596,10 +5586,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122967699</v>
+        <v>122970659</v>
       </c>
       <c r="B50" t="n">
-        <v>90984</v>
+        <v>78781</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5612,34 +5602,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>372504</v>
+        <v>372348</v>
       </c>
       <c r="R50" t="n">
-        <v>6934172</v>
+        <v>6934275</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5698,10 +5688,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122965070</v>
+        <v>122960937</v>
       </c>
       <c r="B51" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5714,42 +5704,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>372491</v>
+        <v>372056</v>
       </c>
       <c r="R51" t="n">
-        <v>6934104</v>
+        <v>6934270</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5805,10 +5790,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122961144</v>
+        <v>122962156</v>
       </c>
       <c r="B52" t="n">
-        <v>74869</v>
+        <v>91001</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5821,21 +5806,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5845,10 +5830,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>372056</v>
+        <v>372213</v>
       </c>
       <c r="R52" t="n">
-        <v>6934270</v>
+        <v>6934190</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5907,10 +5892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122970143</v>
+        <v>122965016</v>
       </c>
       <c r="B53" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5947,10 +5932,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>372099</v>
+        <v>372465</v>
       </c>
       <c r="R53" t="n">
-        <v>6934362</v>
+        <v>6934107</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6009,10 +5994,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122968972</v>
+        <v>122963587</v>
       </c>
       <c r="B54" t="n">
-        <v>74869</v>
+        <v>74875</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6049,10 +6034,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>372261</v>
+        <v>372223</v>
       </c>
       <c r="R54" t="n">
-        <v>6934264</v>
+        <v>6934198</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6111,10 +6096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122963595</v>
+        <v>122968972</v>
       </c>
       <c r="B55" t="n">
-        <v>78775</v>
+        <v>74875</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6127,21 +6112,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6151,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>372223</v>
+        <v>372261</v>
       </c>
       <c r="R55" t="n">
-        <v>6934198</v>
+        <v>6934264</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6213,10 +6198,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122964992</v>
+        <v>122968312</v>
       </c>
       <c r="B56" t="n">
-        <v>74869</v>
+        <v>74875</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6253,10 +6238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>372465</v>
+        <v>372375</v>
       </c>
       <c r="R56" t="n">
-        <v>6934107</v>
+        <v>6934215</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6315,10 +6300,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122967390</v>
+        <v>122965070</v>
       </c>
       <c r="B57" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6331,37 +6316,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>372563</v>
+        <v>372491</v>
       </c>
       <c r="R57" t="n">
-        <v>6934123</v>
+        <v>6934104</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6417,10 +6407,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122960937</v>
+        <v>122969637</v>
       </c>
       <c r="B58" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6457,10 +6447,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>372056</v>
+        <v>372139</v>
       </c>
       <c r="R58" t="n">
-        <v>6934270</v>
+        <v>6934367</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6519,10 +6509,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122968616</v>
+        <v>122969275</v>
       </c>
       <c r="B59" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6555,14 +6545,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>372302</v>
+        <v>372204</v>
       </c>
       <c r="R59" t="n">
-        <v>6934249</v>
+        <v>6934300</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6621,10 +6611,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122969101</v>
+        <v>122969444</v>
       </c>
       <c r="B60" t="n">
-        <v>74869</v>
+        <v>91001</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6637,21 +6627,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6651,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>372244</v>
+        <v>372175</v>
       </c>
       <c r="R60" t="n">
-        <v>6934274</v>
+        <v>6934323</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,10 +6713,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122967374</v>
+        <v>122968306</v>
       </c>
       <c r="B61" t="n">
-        <v>74869</v>
+        <v>82568</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6739,34 +6729,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>372563</v>
+        <v>372375</v>
       </c>
       <c r="R61" t="n">
-        <v>6934123</v>
+        <v>6934215</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6825,10 +6815,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122965447</v>
+        <v>122969955</v>
       </c>
       <c r="B62" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6866,14 +6856,14 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>372613</v>
+        <v>372131</v>
       </c>
       <c r="R62" t="n">
-        <v>6934029</v>
+        <v>6934388</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6932,10 +6922,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122968248</v>
+        <v>122968318</v>
       </c>
       <c r="B63" t="n">
-        <v>90962</v>
+        <v>78781</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6948,21 +6938,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6972,10 +6962,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>372404</v>
+        <v>372375</v>
       </c>
       <c r="R63" t="n">
-        <v>6934224</v>
+        <v>6934215</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,10 +7024,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122968251</v>
+        <v>122965272</v>
       </c>
       <c r="B64" t="n">
-        <v>78775</v>
+        <v>74875</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7050,34 +7040,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>372404</v>
+        <v>372519</v>
       </c>
       <c r="R64" t="n">
-        <v>6934224</v>
+        <v>6934058</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7136,10 +7126,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122960569</v>
+        <v>122968616</v>
       </c>
       <c r="B65" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7176,10 +7166,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>372015</v>
+        <v>372302</v>
       </c>
       <c r="R65" t="n">
-        <v>6934298</v>
+        <v>6934249</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7238,10 +7228,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122970659</v>
+        <v>122963972</v>
       </c>
       <c r="B66" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7274,14 +7264,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hållvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>372348</v>
+        <v>372274</v>
       </c>
       <c r="R66" t="n">
-        <v>6934275</v>
+        <v>6934163</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7340,10 +7330,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122961461</v>
+        <v>122965447</v>
       </c>
       <c r="B67" t="n">
-        <v>74869</v>
+        <v>57487</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7356,37 +7346,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>372167</v>
+        <v>372613</v>
       </c>
       <c r="R67" t="n">
-        <v>6934263</v>
+        <v>6934029</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7442,10 +7437,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122970429</v>
+        <v>122970638</v>
       </c>
       <c r="B68" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7458,37 +7453,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Hållvallen, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>372253</v>
+        <v>372342</v>
       </c>
       <c r="R68" t="n">
-        <v>6934293</v>
+        <v>6934292</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
